--- a/docs/xlsx/jobs-2026-09-09.xlsx
+++ b/docs/xlsx/jobs-2026-09-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="629">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1876 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>2027 Forestry Summer Internship - Farmington ME</t>
+  </si>
+  <si>
+    <t>American Forest Management, Inc.</t>
+  </si>
+  <si>
+    <t>Farmington, ME</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$16 - $18 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-forestry-summer-internship---farmington-me-farmington-maine/9438577272</t>
+  </si>
+  <si>
+    <t>2027 Forestry Summer Internship - Folkston GA</t>
+  </si>
+  <si>
+    <t>Folkston, GA</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$16 - $17 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-forestry-summer-internship---folkston-ga-folkston-georgia/3589338933</t>
+  </si>
+  <si>
+    <t>2027 Forestry Summer Internship - Marianna FL</t>
+  </si>
+  <si>
+    <t>Marianna, FL</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-forestry-summer-internship---marianna-fl-marianna-florida/6331373964</t>
+  </si>
+  <si>
+    <t>2027 Forestry Summer Internship - Waynesboro, TN</t>
+  </si>
+  <si>
+    <t>Waynesboro, TN</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-forestry-summer-internship---waynesboro-tn-waynesboro-tennessee/7178360571</t>
+  </si>
+  <si>
+    <t>2027 Resource Planning &amp; Biometrics Internship</t>
+  </si>
+  <si>
+    <t>Charlotte, NC</t>
+  </si>
+  <si>
+    <t>$18 - $22 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-resource-planning--biometrics-internship-charlotte-north-carolina/4662426355</t>
+  </si>
+  <si>
+    <t>Arkansas Conservation Projects Manager</t>
+  </si>
+  <si>
+    <t>Ozark Land Trust</t>
+  </si>
+  <si>
+    <t>Harrison, AR</t>
+  </si>
+  <si>
+    <t>$48,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-arkansas-conservation-projects-manager-harrison-arkansas/9855855462</t>
+  </si>
+  <si>
+    <t>Assistant Deput Director</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>Santa Rosa, CA</t>
+  </si>
+  <si>
+    <t>$15,263 - $17,336 per month</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-deput-director-santa-rosa-california/2989704356</t>
+  </si>
+  <si>
+    <t>Assistant Field &amp; Project Manager</t>
+  </si>
+  <si>
+    <t>Helia Land Design</t>
+  </si>
+  <si>
+    <t>West Stockbridge, MA</t>
+  </si>
+  <si>
+    <t>$25 - $30 per hour</t>
+  </si>
+  <si>
+    <t>botany-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-installation-team-manager-west-stockbridge-massachusetts/6466838189</t>
+  </si>
+  <si>
+    <t>Bilingual Education &amp; Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>The Land Trust for Santa Barbara County</t>
+  </si>
+  <si>
+    <t>Santa Barbara, CA</t>
+  </si>
+  <si>
+    <t>$74,200 - $79,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-bilingual-education--engagement-coordinator-santa-barbara-california/6929922800</t>
+  </si>
+  <si>
+    <t>Bilingual Farm to School Educator</t>
+  </si>
+  <si>
+    <t>Corvallis Environmental Center</t>
+  </si>
+  <si>
+    <t>Corvallis, OR</t>
+  </si>
+  <si>
+    <t>$18 - $19 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-bilingual-farm-to-school-educator-corvallis-oregon/1552554373</t>
+  </si>
+  <si>
+    <t>Biology &amp; Education Assistant</t>
+  </si>
+  <si>
+    <t>Rainforest Awareness Rescue Education Center - RAREC</t>
+  </si>
+  <si>
+    <t>Iquitos, Lima, Peru, Latin America</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>3 meals per day and accommodations on-site covered, free use of laundry room, wifi and other services</t>
+  </si>
+  <si>
+    <t>environmental-education-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-biology--education-assistant-iquitos-latin-america/3698911495</t>
+  </si>
+  <si>
+    <t>Chemist</t>
+  </si>
+  <si>
+    <t>Azura Consulting LLC</t>
+  </si>
+  <si>
+    <t>Pascagoula, MS</t>
+  </si>
+  <si>
+    <t>$24.12 per hour</t>
+  </si>
+  <si>
+    <t>marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chemist-pascagoula-mississippi/1647240302</t>
+  </si>
+  <si>
+    <t>Community Inclusion Coordinator</t>
+  </si>
+  <si>
+    <t>Chelan-Douglas Land Trust</t>
+  </si>
+  <si>
+    <t>Wenatchee, WA</t>
+  </si>
+  <si>
+    <t>$41,000 - $50,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-inclusion-coordinator-wenatchee-washington/6608142166</t>
+  </si>
+  <si>
+    <t>Ecological Assistant - AmeriCorps</t>
+  </si>
+  <si>
+    <t>Conservation Legacy - Stewards Individual Payments</t>
+  </si>
+  <si>
+    <t>Moose, WY</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$700 per week</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ecological-assistant---americorps-moose-wyoming/9788981400</t>
+  </si>
+  <si>
+    <t>Education Specialist</t>
+  </si>
+  <si>
+    <t>Pacific Whale Foundation</t>
+  </si>
+  <si>
+    <t>Wailuku, HI</t>
+  </si>
+  <si>
+    <t>$58,000 - $63,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-specialist-wailuku-hawaii/6492161770</t>
+  </si>
+  <si>
+    <t>Entomology Insect Curation Volunteer</t>
+  </si>
+  <si>
+    <t>Colorado Natural Heritage Program</t>
+  </si>
+  <si>
+    <t>Fort Collins, CO</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>This is an unpaid, volunteer position</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-entomology-insect-curation-volunteer-fort-collins-colorado/9984769544</t>
+  </si>
+  <si>
+    <t>Environmental Educator (Bilingual)</t>
+  </si>
+  <si>
+    <t>Teatown Lake Reservation</t>
+  </si>
+  <si>
+    <t>Ossining, NY</t>
+  </si>
+  <si>
+    <t>$25/hr</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-bilingual-outreach-instructor-ossining-new-york/5166788027</t>
+  </si>
+  <si>
+    <t>Farallon Volunteer Program- Elephant Seal Research Assistants</t>
+  </si>
+  <si>
+    <t>Point Blue Conservation Science</t>
+  </si>
+  <si>
+    <t>Southeast Farallon Island, CA</t>
+  </si>
+  <si>
+    <t>Unpaid, Volunteer</t>
+  </si>
+  <si>
+    <t>ecology-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-farallon-volunteer-program--elephant-seal-research-assistants-southeast-farallon-island-california/7884556643</t>
+  </si>
+  <si>
+    <t>Forest Fire Response Lead</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources, Division of Forestry</t>
+  </si>
+  <si>
+    <t>Grand Rapids, MN</t>
+  </si>
+  <si>
+    <t>$21.33 - $26.62 / hourly; $44,537 - $55,582 / annually</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-fire-response-lead-grand-rapids-minnesota/8685361315</t>
+  </si>
+  <si>
+    <t>Forest/Fire Ecology Laboratory Technician II</t>
+  </si>
+  <si>
+    <t>University of Florida</t>
+  </si>
+  <si>
+    <t>Milton, FL</t>
+  </si>
+  <si>
+    <t>$19.15 - $24.91 per hour</t>
+  </si>
+  <si>
+    <t>ecology-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestfire-ecology-laboratory-technician-ii-milton-florida/3129694615</t>
+  </si>
+  <si>
+    <t>Forestry Technician</t>
+  </si>
+  <si>
+    <t>Arrowwood Consulting LLC</t>
+  </si>
+  <si>
+    <t>Danville, KY</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-technician-danville-kentucky/6608549451</t>
+  </si>
+  <si>
+    <t>Insectary Technician</t>
+  </si>
+  <si>
+    <t>Lee County Mosquito Control District</t>
+  </si>
+  <si>
+    <t>Lehigh Acres, FL</t>
+  </si>
+  <si>
+    <t>$25.88 - $30.21 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-insectary-technician-lehigh-acres-florida/1090038308</t>
+  </si>
+  <si>
+    <t>Installation Crew Member</t>
+  </si>
+  <si>
+    <t>$19 - $25 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-installation-crew-member-west-stockbridge-massachusetts/6353170046</t>
+  </si>
+  <si>
+    <t>Invasive Plants Tech</t>
+  </si>
+  <si>
+    <t>Grand County Weeds Department</t>
+  </si>
+  <si>
+    <t>Moab, UT</t>
+  </si>
+  <si>
+    <t>$22 - $25 per hour</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-invasive-plants-tech-moab-utah/2960426945</t>
+  </si>
+  <si>
+    <t>Marketing Communications Coordinator</t>
+  </si>
+  <si>
+    <t>South Carolina Aquarium</t>
+  </si>
+  <si>
+    <t>Charleston, SC</t>
+  </si>
+  <si>
+    <t>$44,000 - $48,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marketing-communications-coordinator-charleston-south-carolina/9190931338</t>
+  </si>
+  <si>
+    <t>Nature Programs Educator</t>
+  </si>
+  <si>
+    <t>$18 - $18.75 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nature-programs-educator-corvallis-oregon/1822335142</t>
+  </si>
+  <si>
+    <t>Office Administrative Assistant</t>
+  </si>
+  <si>
+    <t>$22 - $28 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-office-administrative-assistant-west-stockbridge-massachusetts/6769346263</t>
+  </si>
+  <si>
+    <t>Postdoctoral Scientist</t>
+  </si>
+  <si>
+    <t>Conservation Science Partners</t>
+  </si>
+  <si>
+    <t>Truckee, Remote</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>$67,000 - $78,000 per year</t>
+  </si>
+  <si>
+    <t>botany-ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-postdoctoral-scientist-truckee-remote/1670470197</t>
+  </si>
+  <si>
+    <t>Research Associate</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M University- Kingsville</t>
+  </si>
+  <si>
+    <t>Midland, TX</t>
+  </si>
+  <si>
+    <t>Commensurate</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-associate-midland-texas/7136847272</t>
+  </si>
+  <si>
+    <t>Nacogdoches, TX</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-associate-nacogdoches-texas/9132249894</t>
+  </si>
+  <si>
+    <t>Restoration Project Specialist</t>
+  </si>
+  <si>
+    <t>Central Coast Wetlands Group and Coastal Conservation and Research</t>
+  </si>
+  <si>
+    <t>Moss Landing, CA</t>
+  </si>
+  <si>
+    <t>$28 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-project-specialist-moss-landing-california/5003131339</t>
+  </si>
+  <si>
+    <t>Senior Development Director</t>
+  </si>
+  <si>
+    <t>Environmental League of Massachusetts</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>$85,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-development-director-boston-massachusetts/1267855565</t>
+  </si>
+  <si>
+    <t>Software Engineer, Biodiversity Platforms</t>
+  </si>
+  <si>
+    <t>American Bird Conservancy</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>Estimated at $117,000 - $130,000*; Based on experience.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-software-engineer-biodiversity-platforms-remote-remote/4940858470</t>
+  </si>
+  <si>
+    <t>Stormwater Management Inspector</t>
+  </si>
+  <si>
+    <t>Cecil County, MD</t>
+  </si>
+  <si>
+    <t>Elkton, MD</t>
+  </si>
+  <si>
+    <t>$27.66 - $29.04 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stormwater-management-inspector-elkton-maryland/9436432718</t>
+  </si>
+  <si>
+    <t>Supervisor I, Natural Resource Management</t>
+  </si>
+  <si>
+    <t>San Jose Conservation Corps + Charter School</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>$29.50 - $32.64 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-supervisor-i-natural-resource-management-san-jose-california/1969526171</t>
+  </si>
+  <si>
+    <t>Supervisor I, Zero Waste</t>
+  </si>
+  <si>
+    <t>admin-leadership-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-zero-waste-commercial-driver-san-jose-california/7105731365</t>
+  </si>
+  <si>
+    <t>Vice President &amp; Chief Research Officer</t>
+  </si>
+  <si>
+    <t>Desert Botanical Garden</t>
+  </si>
+  <si>
+    <t>Phoenix, AZ</t>
+  </si>
+  <si>
+    <t>$168,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vice-president--chief-research-officer-phoenix-arizona/3845799550</t>
+  </si>
+  <si>
+    <t>Walking Mountains Graduate Fellowship 2027-2029</t>
+  </si>
+  <si>
+    <t>Walking Mountains</t>
+  </si>
+  <si>
+    <t>Avon, CO</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$17,500 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-walking-mountains-graduate-fellowship-2027-2029-avon-colorado/7177344828</t>
+  </si>
+  <si>
+    <t>Water Resource Control Engineer</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$6,488 - $12,152 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resource-control-engineer-sacramento-california/5584204985</t>
+  </si>
+  <si>
+    <t>Watershed &amp; Waste Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>I Love A Clean San Diego</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>$22 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed--waste-coordinator-san-diego-california/1290812858</t>
+  </si>
+  <si>
+    <t>Wetland Conservation Education Landscape Analysis RFP</t>
+  </si>
+  <si>
+    <t>National Geographic Society</t>
+  </si>
+  <si>
+    <t>Washington, DC, Remote</t>
+  </si>
+  <si>
+    <t>$20,000</t>
+  </si>
+  <si>
+    <t>environmental-education-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wetland-conservation-education-landscape-analysis-rfp-washington-dc-remote/6716402714</t>
+  </si>
+  <si>
+    <t>Wildlife Caretaker Assistant</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-caretaker-assistant-iquitos-latin-america/5866487505</t>
+  </si>
+  <si>
+    <t>Wildlife Laboratory Technician</t>
+  </si>
+  <si>
+    <t>Matson's Laboratory</t>
+  </si>
+  <si>
+    <t>Manhattan, MT</t>
+  </si>
+  <si>
+    <t>$17.05 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-laboratory-technician-manhattan-montana/3317301152</t>
+  </si>
+  <si>
+    <t>Wildlife Veterinarian</t>
+  </si>
+  <si>
+    <t>$400 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-veterinarian-iquitos-latin-america/3598433566</t>
+  </si>
+  <si>
+    <t>Year-Round Field Crew Member: Virginia</t>
+  </si>
+  <si>
+    <t>Southern Appalachian Wilderness Stewards (SAWS)</t>
+  </si>
+  <si>
+    <t>Roanoke, VA</t>
+  </si>
+  <si>
+    <t>$21 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-year-round-field-crew-member-virginia-roanoke-virginia/4905956714</t>
+  </si>
+  <si>
+    <t>🌍 Líder de Equipo F2F | Donantes Individuales | Turno Mañana o Tarde | CABA</t>
+  </si>
+  <si>
+    <t>Ingeniería Sin Fronteras Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b99418092714cbdaa62294455b4b046-lider-de-equipo-f2f-donantes-individuales-turno-manana-o-tarde-caba-ingenieria-sin-fronteras-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Accounting Associate</t>
+  </si>
+  <si>
+    <t>Japan Society</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1424d51eb8e349dba3889e7b56fc9684-accounting-associate-japan-society-new-york</t>
+  </si>
+  <si>
+    <t>Administrative Assistant Membership &amp; Audience Services</t>
+  </si>
+  <si>
+    <t>Maine Public Broadcasting</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 22.75/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f36cdd16b0ef4f79be1581ece36bc7fd-administrative-assistant-membership-audience-services-maine-public-broadcasting-portland</t>
+  </si>
+  <si>
+    <t>ASESOR(A) EDUCADOR(A) COMINUTARIO(A)</t>
+  </si>
+  <si>
+    <t>Médicos Sin Fronteras en México AC</t>
+  </si>
+  <si>
+    <t>Chilpancingo de los Bravo, Guerrero, MX</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>MXN 17000.00 - 17900.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f98bdfb1d2a246859a9dc99f135fcab1-asesora-educadora-cominutarioa-medicos-sin-fronteras-en-mexico-ac-chilpancingo-de-los-bravo</t>
+  </si>
+  <si>
+    <t>Bilingual Legal Advocate</t>
+  </si>
+  <si>
+    <t>Sexual Assault Legal Institute</t>
+  </si>
+  <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>USD 49000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Legal Assistance, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74dc1f460d7942448ed4755df8049f3d-bilingual-legal-advocate-sexual-assault-legal-institute-silver-spring</t>
+  </si>
+  <si>
+    <t>Canvasser - CA Calls Yes on 3, No on 39</t>
+  </si>
+  <si>
+    <t>KIWA (Koreatown Immigrant Workers Alliance)</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79fa5fc28cf34d2c90156c17232ab34b-canvasser-ca-calls-yes-on-3-no-on-39-kiwa-koreatown-immigrant-workers-alliance-los-angeles</t>
+  </si>
+  <si>
+    <t>Captador/a de Fondos en vía pública - Córdoba (Capital)</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS Argentina</t>
+  </si>
+  <si>
+    <t>Córdoba, Córdoba, AR</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>Community Development, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b913b15dbb94886a47871b83ea3eb3e-captadora-de-fondos-en-via-publica-cordoba-capital-aldeas-infantiles-sos-argentina-cordoba</t>
+  </si>
+  <si>
+    <t>Captadores/as de Fondos en vía pública para CABA + Zona Oeste</t>
+  </si>
+  <si>
+    <t>Community Development, Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d7850b9e5dd420296be82c83551cfc9-captadoresas-de-fondos-en-via-publica-para-caba-zona-oeste-aldeas-infantiles-sos-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>Proactive Community Services</t>
+  </si>
+  <si>
+    <t>Flossmoor, Illinois</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Job Workplace, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1748108dc9640808684e7d06a952e4b-case-manager-proactive-community-services-flossmoor</t>
+  </si>
+  <si>
+    <t>Chief, Community Leadership &amp; Training Institute</t>
+  </si>
+  <si>
+    <t>NYC Kids RISE</t>
+  </si>
+  <si>
+    <t>Long Island City, New York</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 250000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdb4b9fa5c8d4660a66ca6baf0f13f66-chief-community-leadership-training-institute-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
+    <t>Community Engagement Director</t>
+  </si>
+  <si>
+    <t>Maine Equal Justice</t>
+  </si>
+  <si>
+    <t>Augusta, ME</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Hunger Food Security, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/805da3f3ee51434eb2ab357aa21f7e53-community-engagement-director-maine-equal-justice-augusta</t>
+  </si>
+  <si>
+    <t>Community Resource Navigator</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Poverty, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d55e7a9501bb4a06a2544f7a2f70f5ef-community-resource-navigator-proactive-community-services-flossmoor</t>
+  </si>
+  <si>
+    <t>Coordinador/a de Comunicación</t>
+  </si>
+  <si>
+    <t>Constru Casa</t>
+  </si>
+  <si>
+    <t>Antigua Guatemala, Sacatepéquez, GT</t>
+  </si>
+  <si>
+    <t>GTQ 4500.00 - 5000.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba02c412570e48539380246a309cb8be-coordinadora-de-comunicacion-constru-casa-antigua-guatemala</t>
+  </si>
+  <si>
+    <t>Coordinador/a de Voluntariado</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/baacb29cc85c4afab496bdd9076fdcbc-coordinadora-de-voluntariado-constru-casa-antigua-guatemala</t>
+  </si>
+  <si>
+    <t>Coordinator, Finance</t>
+  </si>
+  <si>
+    <t>Share Our Strength</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Poverty, Children Youth, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa11aa8e92d04d3d9c5c619efa75d9d0-coordinator-finance-share-our-strength-washington</t>
+  </si>
+  <si>
+    <t>Creative Digital Content Strategist</t>
+  </si>
+  <si>
+    <t>Advancement Project</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 87700.00/year</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eb2790ea40a041718acd1530c8f1e11e-creative-digital-content-strategist-advancement-project-washington</t>
+  </si>
+  <si>
+    <t>Data Collector</t>
+  </si>
+  <si>
+    <t>Harvard T.H. Chan School of Public Health</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a833caba93914482ac1bdcaa3f5cc158-data-collector-harvard-th-chan-school-of-public-health-boston</t>
+  </si>
+  <si>
+    <t>Deputy Director of Government Affairs - Hybrid Sacramento CA</t>
+  </si>
+  <si>
+    <t>California Primary Care Association</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/56ac2e394b8946ee851734b49b85aa24-deputy-director-of-government-affairs-hybrid-sacramento-ca-california-primary-care-association-sacramento</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Marin County Bicycle Coalition</t>
+  </si>
+  <si>
+    <t>Fairfax, CA</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6177120f36154f3982af8cac86124ef8-development-manager-marin-county-bicycle-coalition-fairfax</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT OPERATIONS MANAGER</t>
+  </si>
+  <si>
+    <t>Signature Theatre</t>
+  </si>
+  <si>
+    <t>Arlington, VA</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c35891b98d3e40c9afd55976b44a3dce-development-operations-manager-signature-theatre-arlington</t>
+  </si>
+  <si>
+    <t>Digital Marketing &amp; Funrdraising Consultant</t>
+  </si>
+  <si>
+    <t>iMission Institute</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 45.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1a9be73ba23c4777a006e0949fcd3420-digital-marketing-funrdraising-consultant-imission-institute-new-haven</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Maryland Center on Economic Policy</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Policy, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a660a47130564c138b6186854df6bb3a-director-of-development-maryland-center-on-economic-policy-baltimore</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>Open Doors for Refugees</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Volunteering, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f33a77ffe89455c9b793e4615d80cb8-director-of-programs-open-doors-for-refugees-madison</t>
+  </si>
+  <si>
+    <t>Director of Workforce Services</t>
+  </si>
+  <si>
+    <t>The Lamb Center</t>
+  </si>
+  <si>
+    <t>Fairfax, Virginia</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c0341b8799745059fca69dada08840b-director-of-workforce-services-the-lamb-center-fairfax</t>
+  </si>
+  <si>
+    <t>Director, Do What You Love</t>
+  </si>
+  <si>
+    <t>Alzheimer's Association, Massachusetts / New Hampshire Chapter</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e9aa17c4de54494a593237a1e2408b3-director-do-what-you-love-alzheimers-association-massachusetts-new-hampshire-chapter-san-jose</t>
+  </si>
+  <si>
+    <t>Director, Technology &amp; Information Systems</t>
+  </si>
+  <si>
+    <t>The Breast Cancer Research Foundation</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Job Workplace, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/960e6ab7755c472db688f2abbbde0291-director-technology-information-systems-the-breast-cancer-research-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Disbursement Associate</t>
+  </si>
+  <si>
+    <t>The Ford Foundation</t>
+  </si>
+  <si>
+    <t>USD 103000.00 - 103000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/903c324d136042e4821a0bbc29e60627-disbursement-associate-the-ford-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Education Coordinator</t>
+  </si>
+  <si>
+    <t>Hunterdon Art Museum</t>
+  </si>
+  <si>
+    <t>Clinton, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca4f8f2420884a55b15b5e515256fbb4-education-coordinator-hunterdon-art-museum-clinton</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Lake City Partners Ending Homelessness</t>
+  </si>
+  <si>
+    <t>Shoreline, Washington</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5491bacbc48a4f609796d0371b2624c2-executive-director-lake-city-partners-ending-homelessness-shoreline</t>
+  </si>
+  <si>
+    <t>Family Advocacy Unit Staff Attorney</t>
+  </si>
+  <si>
+    <t>Community Legal Services, Inc.</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46ab478d93d248029ce3f284718e4286-family-advocacy-unit-staff-attorney-community-legal-services-inc-philadelphia</t>
+  </si>
+  <si>
+    <t>Family Intervention Specialist (In Home Family Therapy)</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Pittsfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/001a81e1aba34a9ea699a91a246cad27-family-intervention-specialist-in-home-family-therapy-youth-villages-pittsfield</t>
+  </si>
+  <si>
+    <t>Family Intervention Specialist (In Home Therapy)</t>
+  </si>
+  <si>
+    <t>Manchester, New Hampshire</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 86000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54564d0b36a5440d93c4f67afbfe17d2-family-intervention-specialist-in-home-therapy-youth-villages-manchester</t>
+  </si>
+  <si>
+    <t>Augusta, Maine</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e0af5e5d7f54eeea3122a26e19a6104-family-intervention-specialist-in-home-therapy-youth-villages-augusta</t>
+  </si>
+  <si>
+    <t>Family Literacy Program Coordinator</t>
+  </si>
+  <si>
+    <t>ILLINOIS WORKERS IN ACTION</t>
+  </si>
+  <si>
+    <t>Bolingbrook, Illinois</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b1dffa1869548a2b1814f3bfec81aef-family-literacy-program-coordinator-illinois-workers-in-action-bolingbrook</t>
+  </si>
+  <si>
+    <t>Florida Early Learning Tutor</t>
+  </si>
+  <si>
+    <t>Ampact</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>USD 950.00 - 950.00/week</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6209bea99e7e4400b7e5fe7f85b89be7-florida-early-learning-tutor-ampact-miami</t>
+  </si>
+  <si>
+    <t>Head of Mission - Syria</t>
+  </si>
+  <si>
+    <t>INTERSOS</t>
+  </si>
+  <si>
+    <t>Damascus, Damascus Governorate, SY</t>
+  </si>
+  <si>
+    <t>EUR 4505.00 - 5182.00/month</t>
+  </si>
+  <si>
+    <t>International Relations, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a621ca742a34c85a693731576c21656-head-of-mission-syria-intersos-damascus</t>
+  </si>
+  <si>
+    <t>Health and Independence Unit Staff Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d1d1c3f204fa4537abacf3dd4c05af45-health-and-independence-unit-staff-attorney-community-legal-services-inc-philadelphia</t>
+  </si>
+  <si>
+    <t>Home Tutors – Hyderabad &amp; Telangana</t>
+  </si>
+  <si>
+    <t>Shiva's Tutorial</t>
+  </si>
+  <si>
+    <t>Hyderabad, Telangana, IN</t>
+  </si>
+  <si>
+    <t>USD 5.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a4d3fc62eff47bf92069f74c888dc75-home-tutors-hyderabad-telangana-shivas-tutorial-hyderabad</t>
+  </si>
+  <si>
+    <t>Housing Navigator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7dcf603b49a647249b376eb29f13cd9a-housing-navigator-proactive-community-services-flossmoor</t>
+  </si>
+  <si>
+    <t>Labor &amp; Immigration Organizer</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13b709f04d13404ca18e9a516dc83777-labor-immigration-organizer-illinois-workers-in-action-chicago</t>
+  </si>
+  <si>
+    <t>Learning and Development Specialist</t>
+  </si>
+  <si>
+    <t>Heading Home Inc.</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/711f1f5d6e354ed8aed7c16048a4471f-learning-and-development-specialist-heading-home-inc-boston</t>
+  </si>
+  <si>
+    <t>Licensed Assessment Counselor</t>
+  </si>
+  <si>
+    <t>Bartlett, Tennessee</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d7f676c3e93d42aab8cd6ebe905f155d-licensed-assessment-counselor-youth-villages-bartlett</t>
+  </si>
+  <si>
+    <t>Lifecycle Marketing Fundraising Manager</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c4e8d3763054daeb6e697aeba1c29e7-lifecycle-marketing-fundraising-manager-the-breast-cancer-research-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Looking to hire a Full time and/or Part time Community Care Associate</t>
+  </si>
+  <si>
+    <t>Loudoun Hunger Relief</t>
+  </si>
+  <si>
+    <t>Leesburg, Virginia</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/051dba3e60ac4acfa4b15e59f164a133-looking-to-hire-a-full-time-andor-part-time-community-care-associate-loudoun-hunger-relief-leesburg</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>WaterAid America</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60af3e8660824260a7c7571dcc3c17df-major-gifts-officer-wateraid-america-new-york</t>
+  </si>
+  <si>
+    <t>American Indian College Fund</t>
+  </si>
+  <si>
+    <t>Remote (Colorado)</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff87aa5465c24058938ae47426b3ef94-major-gifts-officer-american-indian-college-fund-denver</t>
+  </si>
+  <si>
+    <t>Managing Director, Gift Planning (Legacy Giving)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/89cb234b4feb4247b699fa36e6288e96-managing-director-gift-planning-legacy-giving-the-breast-cancer-research-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Membership &amp; Community Partnerships Coordinator</t>
+  </si>
+  <si>
+    <t>New York Disaster Interfaith Services (NYDIS)</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Religion Spirituality, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1262f3d123714f75bd1d898fd4a36a0a-membership-community-partnerships-coordinator-new-york-disaster-interfaith-services-nydis-new-york</t>
+  </si>
+  <si>
+    <t>Membership Recruitment Specialist</t>
+  </si>
+  <si>
+    <t>Girl Scout Council of the Nation's Capital</t>
+  </si>
+  <si>
+    <t>Manassas, Virginia</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a3723bb653049f4b3988fb485fc5463-membership-recruitment-specialist-girl-scout-council-of-the-nations-capital-manassas</t>
+  </si>
+  <si>
+    <t>Nonprofit Fundraising Manager</t>
+  </si>
+  <si>
+    <t>Achieve Miami, Inc</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55159f32fd6944e6acfb6f6f4696af3e-nonprofit-fundraising-manager-achieve-miami-inc-miami</t>
+  </si>
+  <si>
+    <t>Operations Coordinator - Genetics &amp; Genomics Research Labs</t>
+  </si>
+  <si>
+    <t>Icahn School of Medicine at Mount Sinai, Department of Genetics and Genomic Sciences</t>
+  </si>
+  <si>
+    <t>USD 66482.07 - 74250.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/108217d2fc134a4498403cd36b413e24-operations-coordinator-genetics-genomics-research-labs-icahn-school-of-medicine-at-mount-sinai-department-of-genetics-and-genomic-sciences-new-york</t>
+  </si>
+  <si>
+    <t>Principal Health Inspector</t>
+  </si>
+  <si>
+    <t>Boston Public Health Commission</t>
+  </si>
+  <si>
+    <t>USD 1542.30 - 2237.51/week</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f2d1666d7654270aeec639645ce04aa-principal-health-inspector-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Profesional en Derecho Ambiental y Calidad del Aire (Perú)</t>
+  </si>
+  <si>
+    <t>Interamerican Association for Environmental Defense (AIDA)</t>
+  </si>
+  <si>
+    <t>Remote (PE)</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37577aca593546c9b5701f26d9906786-profesional-en-derecho-ambiental-y-calidad-del-aire-peru-interamerican-association-for-environmental-defense-aida-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Program Coordinator (APT)</t>
+  </si>
+  <si>
+    <t>American Association of Colleges and Universities</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e67817fdc8a84af4a6bce132140d8c9c-program-coordinator-apt-american-association-of-colleges-and-universities-washington</t>
+  </si>
+  <si>
+    <t>Program Coordinator (OLS)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65e63360288f4d8cb8cf6a095635ea31-program-coordinator-ols-american-association-of-colleges-and-universities-washington</t>
+  </si>
+  <si>
+    <t>Program Director - Entre Familia</t>
+  </si>
+  <si>
+    <t>USD 93000.00 - 103000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63fc346f1fbe43a6b0cf5217717fa475-program-director-entre-familia-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Jewish Community Center Sonoma County</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Seniors Retirement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de0e254d6ac74aad9670ceb83163345c-program-manager-jewish-community-center-sonoma-county-santa-rosa</t>
+  </si>
+  <si>
+    <t>Program Officer</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/14ec069e689343e09a2d7e8e32e041ad-program-officer-american-indian-college-fund-denver</t>
+  </si>
+  <si>
+    <t>Program Support Specialist</t>
+  </si>
+  <si>
+    <t>Aurora, Illinois</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e572b723d1a249ec9dfb8071f956e816-program-support-specialist-illinois-workers-in-action-aurora</t>
+  </si>
+  <si>
+    <t>Project Assistant, Social Services Job Training Program – Chicago, IL region (Temporary)</t>
+  </si>
+  <si>
+    <t>Hunger Free America</t>
+  </si>
+  <si>
+    <t>USD 25.82 - 25.82/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a78bd698ac540e789721a3a12fa2a2d-project-assistant-social-services-job-training-program-chicago-il-region-temporary-hunger-free-america-chicago</t>
+  </si>
+  <si>
+    <t>Revenue Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Partnership to End Addiction</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b605f6f59fea4bbd84a185fbaf4551e8-revenue-operations-coordinator-partnership-to-end-addiction-new-york</t>
+  </si>
+  <si>
+    <t>Senior Consultant, Strategic Communications Project Management</t>
+  </si>
+  <si>
+    <t>BME Strategies</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/e02253f81b104539bf981ecdfd55f0f9-senior-consultant-strategic-communications-project-management-bme-strategies-north-andover</t>
+  </si>
+  <si>
+    <t>Senior Development Coordinator</t>
+  </si>
+  <si>
+    <t>National Parks Conservation Association</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6beb0a362954e1eae1bbcae133ca839-senior-development-coordinator-national-parks-conservation-association-washington</t>
+  </si>
+  <si>
+    <t>Senior Executive Assistant</t>
+  </si>
+  <si>
+    <t>Interfaith America</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Religion Spirituality, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e468fa527304eedbbab36f864505216-senior-executive-assistant-interfaith-america-chicago</t>
+  </si>
+  <si>
+    <t>Senior Philanthropy Officer (Major Gifts Officer)</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science, Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e27ebefd2c54a0fba4bf6bbb6233e0f-senior-philanthropy-officer-major-gifts-officer-the-breast-cancer-research-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Seniors Helping Seniors - Help Seniors Stay Home Where They Belong (Beach Cities-South Bay, Torrance, Palos Verdes, San Pedro, El Segundo)</t>
+  </si>
+  <si>
+    <t>Seniors Helping Seniors South Bay</t>
+  </si>
+  <si>
+    <t>Torrance, California</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/a8f55b8cfa1a4938a146d535c9b1e2dd-seniors-helping-seniors-help-seniors-stay-home-where-they-belong-beach-cities-south-bay-torrance-palos-verdes-san-pedro-el-segundo-seniors-helping-seniors-south-bay-torrance</t>
+  </si>
+  <si>
+    <t>Special Events Officer</t>
+  </si>
+  <si>
+    <t>Rising Ground</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d1385ee9aca423eb5e9c58a7239cb6c-special-events-officer-rising-ground-new-york</t>
+  </si>
+  <si>
+    <t>Special Gifts Officer</t>
+  </si>
+  <si>
+    <t>Catlin Gabel School</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c59ae1d09d944aa582bf87876ee1c471-special-gifts-officer-catlin-gabel-school-portland</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>Chicago Lawyers' Committee For Civil Rights Under Law, Inc.</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Legal Assistance, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/876bf0e5d5f54fe0aedc3ca7f4a64b96-staff-accountant-chicago-lawyers-committee-for-civil-rights-under-law-inc-chicago</t>
+  </si>
+  <si>
+    <t>Staff Accountant - Grants and Compliance</t>
+  </si>
+  <si>
+    <t>Everyone On</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62783c67e562449a9babe9da8fa75540-staff-accountant-grants-and-compliance-everyone-on-los-angeles</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Family Defense, Queens</t>
+  </si>
+  <si>
+    <t>Center for Family Representation, Inc.</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 86800.00 - 122800.00/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/079c8ed916b34b26b905c75ad2a64237-staff-attorney-family-defense-queens-center-for-family-representation-inc-queens-county</t>
+  </si>
+  <si>
+    <t>Strings &amp; Orchestra Program Manager</t>
+  </si>
+  <si>
+    <t>Merit School of Music</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>USD 50000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c09219377dee45be87fcf421c6b1444c-strings-orchestra-program-manager-merit-school-of-music-chicago</t>
+  </si>
+  <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>Immigration Center for Women and Children</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Family, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26dc0502e3e64754b51b0710f78e132b-supervising-attorney-immigration-center-for-women-and-children-los-angeles</t>
+  </si>
+  <si>
+    <t>US Audience Growth Consultant</t>
+  </si>
+  <si>
+    <t>350.org</t>
+  </si>
+  <si>
+    <t>Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a854b0a06bf14c58ba7fc821ae0937b8-us-audience-growth-consultant-350org-washington</t>
+  </si>
+  <si>
+    <t>Vice President for Ocean Conservation</t>
+  </si>
+  <si>
+    <t>The Conservation Law Foundation</t>
+  </si>
+  <si>
+    <t>USD 136000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8242de09088b463b851e81a2f69108d2-vice-president-for-ocean-conservation-the-conservation-law-foundation-boston</t>
+  </si>
+  <si>
+    <t>Vice President of Community Engagement</t>
+  </si>
+  <si>
+    <t>Conservation Colorado</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef716bf1c0ce48fb957e74159f7ca20c-vice-president-of-community-engagement-conservation-colorado-denver</t>
+  </si>
+  <si>
+    <t>Voter Contact Field Director</t>
+  </si>
+  <si>
+    <t>The Outreach Team</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 1146.00 - 1500.00/week</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/ef9c70c70d214fa092bf3229551b94f4-voter-contact-field-director-the-outreach-team-minneapolis</t>
+  </si>
+  <si>
+    <t>Youth Educator, PS 179</t>
+  </si>
+  <si>
+    <t>East Side House Settlement</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aec14a53539e4ea1abe612accd23e04c-youth-educator-ps-179-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>Zona Córdoba (capital) - Líder de Equipo de Captadores/as de Fondos</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/676719bd555e4b159950413b7c2b54d6-zona-cordoba-capital-lider-de-equipo-de-captadoresas-de-fondos-aldeas-infantiles-sos-argentina-cordoba</t>
+  </si>
+  <si>
+    <t>Zona: Mar del Plata - Lider de Equipo de Captadores/as de Fondos (F2F)</t>
+  </si>
+  <si>
+    <t>Mar del Plata, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f66d1a6fc14f463689b0dd27ff926118-zona-mar-del-plata-lider-de-equipo-de-captadoresas-de-fondos-f2f-aldeas-infantiles-sos-argentina-mar-del-plata</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1917,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1943,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2325,1090 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" t="s">
+        <v>97</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" t="s">
+        <v>133</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" t="s">
+        <v>145</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" t="s">
+        <v>149</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" t="s">
+        <v>153</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29" t="s">
+        <v>158</v>
+      </c>
+      <c r="E29" t="s">
+        <v>159</v>
+      </c>
+      <c r="F29" t="s">
+        <v>160</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C30" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C31" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" t="s">
+        <v>84</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>169</v>
+      </c>
+      <c r="B32" t="s">
+        <v>170</v>
+      </c>
+      <c r="C32" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" t="s">
+        <v>133</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" t="s">
+        <v>145</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>182</v>
+      </c>
+      <c r="F34" t="s">
+        <v>145</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>187</v>
+      </c>
+      <c r="F35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" t="s">
+        <v>192</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>193</v>
+      </c>
+      <c r="F36" t="s">
+        <v>194</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" t="s">
+        <v>191</v>
+      </c>
+      <c r="C37" t="s">
+        <v>192</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>202</v>
+      </c>
+      <c r="F38" t="s">
+        <v>84</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>204</v>
+      </c>
+      <c r="B39" t="s">
+        <v>205</v>
+      </c>
+      <c r="C39" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" t="s">
+        <v>207</v>
+      </c>
+      <c r="E39" t="s">
+        <v>208</v>
+      </c>
+      <c r="F39" t="s">
+        <v>58</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>210</v>
+      </c>
+      <c r="B40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" t="s">
+        <v>211</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F40" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>214</v>
+      </c>
+      <c r="B41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C41" t="s">
+        <v>216</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>217</v>
+      </c>
+      <c r="F41" t="s">
+        <v>218</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>220</v>
+      </c>
+      <c r="B42" t="s">
+        <v>221</v>
+      </c>
+      <c r="C42" t="s">
+        <v>222</v>
+      </c>
+      <c r="D42" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" t="s">
+        <v>223</v>
+      </c>
+      <c r="F42" t="s">
+        <v>224</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>226</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" t="s">
+        <v>227</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>229</v>
+      </c>
+      <c r="B44" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" t="s">
+        <v>231</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>232</v>
+      </c>
+      <c r="F44" t="s">
+        <v>97</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>234</v>
+      </c>
+      <c r="B45" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>235</v>
+      </c>
+      <c r="F45" t="s">
+        <v>227</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>237</v>
+      </c>
+      <c r="B46" t="s">
+        <v>238</v>
+      </c>
+      <c r="C46" t="s">
+        <v>239</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>240</v>
+      </c>
+      <c r="F46" t="s">
+        <v>241</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3464,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3503,1930 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" t="s">
+        <v>255</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F5" t="s">
+        <v>267</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F7" t="s">
+        <v>280</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D8" t="s">
+        <v>285</v>
+      </c>
+      <c r="E8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>288</v>
+      </c>
+      <c r="B9" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D9" t="s">
+        <v>285</v>
+      </c>
+      <c r="E9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F9" t="s">
+        <v>289</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" t="s">
+        <v>294</v>
+      </c>
+      <c r="F10" t="s">
+        <v>295</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>297</v>
+      </c>
+      <c r="B11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" t="s">
+        <v>299</v>
+      </c>
+      <c r="D11" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" t="s">
+        <v>300</v>
+      </c>
+      <c r="F11" t="s">
+        <v>301</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>303</v>
+      </c>
+      <c r="B12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D12" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" t="s">
+        <v>306</v>
+      </c>
+      <c r="F12" t="s">
+        <v>307</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>309</v>
+      </c>
+      <c r="B13" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" t="s">
+        <v>310</v>
+      </c>
+      <c r="F13" t="s">
+        <v>311</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>313</v>
+      </c>
+      <c r="B14" t="s">
+        <v>314</v>
+      </c>
+      <c r="C14" t="s">
+        <v>315</v>
+      </c>
+      <c r="D14" t="s">
+        <v>253</v>
+      </c>
+      <c r="E14" t="s">
+        <v>316</v>
+      </c>
+      <c r="F14" t="s">
+        <v>317</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>319</v>
+      </c>
+      <c r="B15" t="s">
+        <v>314</v>
+      </c>
+      <c r="C15" t="s">
+        <v>315</v>
+      </c>
+      <c r="D15" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" t="s">
+        <v>316</v>
+      </c>
+      <c r="F15" t="s">
+        <v>317</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>321</v>
+      </c>
+      <c r="B16" t="s">
+        <v>322</v>
+      </c>
+      <c r="C16" t="s">
+        <v>323</v>
+      </c>
+      <c r="D16" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" t="s">
+        <v>324</v>
+      </c>
+      <c r="F16" t="s">
+        <v>325</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>327</v>
+      </c>
+      <c r="B17" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" t="s">
+        <v>329</v>
+      </c>
+      <c r="D17" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" t="s">
+        <v>330</v>
+      </c>
+      <c r="F17" t="s">
+        <v>331</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>333</v>
+      </c>
+      <c r="B18" t="s">
+        <v>334</v>
+      </c>
+      <c r="C18" t="s">
+        <v>335</v>
+      </c>
+      <c r="D18" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" t="s">
+        <v>336</v>
+      </c>
+      <c r="F18" t="s">
+        <v>337</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>339</v>
+      </c>
+      <c r="B19" t="s">
+        <v>340</v>
+      </c>
+      <c r="C19" t="s">
+        <v>341</v>
+      </c>
+      <c r="D19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E19" t="s">
+        <v>247</v>
+      </c>
+      <c r="F19" t="s">
+        <v>247</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>343</v>
+      </c>
+      <c r="B20" t="s">
+        <v>344</v>
+      </c>
+      <c r="C20" t="s">
+        <v>345</v>
+      </c>
+      <c r="D20" t="s">
+        <v>253</v>
+      </c>
+      <c r="E20" t="s">
+        <v>346</v>
+      </c>
+      <c r="F20" t="s">
+        <v>347</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>349</v>
+      </c>
+      <c r="B21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C21" t="s">
+        <v>351</v>
+      </c>
+      <c r="D21" t="s">
+        <v>253</v>
+      </c>
+      <c r="E21" t="s">
+        <v>352</v>
+      </c>
+      <c r="F21" t="s">
+        <v>353</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>355</v>
+      </c>
+      <c r="B22" t="s">
+        <v>356</v>
+      </c>
+      <c r="C22" t="s">
+        <v>357</v>
+      </c>
+      <c r="D22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E22" t="s">
+        <v>358</v>
+      </c>
+      <c r="F22" t="s">
+        <v>247</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>360</v>
+      </c>
+      <c r="B23" t="s">
+        <v>361</v>
+      </c>
+      <c r="C23" t="s">
+        <v>362</v>
+      </c>
+      <c r="D23" t="s">
+        <v>253</v>
+      </c>
+      <c r="E23" t="s">
+        <v>363</v>
+      </c>
+      <c r="F23" t="s">
+        <v>364</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>366</v>
+      </c>
+      <c r="B24" t="s">
+        <v>367</v>
+      </c>
+      <c r="C24" t="s">
+        <v>368</v>
+      </c>
+      <c r="D24" t="s">
+        <v>253</v>
+      </c>
+      <c r="E24" t="s">
+        <v>369</v>
+      </c>
+      <c r="F24" t="s">
+        <v>370</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>372</v>
+      </c>
+      <c r="B25" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" t="s">
+        <v>374</v>
+      </c>
+      <c r="D25" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" t="s">
+        <v>346</v>
+      </c>
+      <c r="F25" t="s">
+        <v>375</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>377</v>
+      </c>
+      <c r="B26" t="s">
+        <v>378</v>
+      </c>
+      <c r="C26" t="s">
+        <v>379</v>
+      </c>
+      <c r="D26" t="s">
+        <v>253</v>
+      </c>
+      <c r="E26" t="s">
+        <v>380</v>
+      </c>
+      <c r="F26" t="s">
+        <v>247</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>382</v>
+      </c>
+      <c r="B27" t="s">
+        <v>383</v>
+      </c>
+      <c r="C27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D27" t="s">
+        <v>253</v>
+      </c>
+      <c r="E27" t="s">
+        <v>385</v>
+      </c>
+      <c r="F27" t="s">
+        <v>386</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>388</v>
+      </c>
+      <c r="B28" t="s">
+        <v>389</v>
+      </c>
+      <c r="C28" t="s">
+        <v>384</v>
+      </c>
+      <c r="D28" t="s">
+        <v>253</v>
+      </c>
+      <c r="E28" t="s">
+        <v>390</v>
+      </c>
+      <c r="F28" t="s">
+        <v>391</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>393</v>
+      </c>
+      <c r="B29" t="s">
+        <v>394</v>
+      </c>
+      <c r="C29" t="s">
+        <v>395</v>
+      </c>
+      <c r="D29" t="s">
+        <v>253</v>
+      </c>
+      <c r="E29" t="s">
+        <v>396</v>
+      </c>
+      <c r="F29" t="s">
+        <v>397</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>399</v>
+      </c>
+      <c r="B30" t="s">
+        <v>400</v>
+      </c>
+      <c r="C30" t="s">
+        <v>401</v>
+      </c>
+      <c r="D30" t="s">
+        <v>253</v>
+      </c>
+      <c r="E30" t="s">
+        <v>402</v>
+      </c>
+      <c r="F30" t="s">
+        <v>403</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>405</v>
+      </c>
+      <c r="B31" t="s">
+        <v>406</v>
+      </c>
+      <c r="C31" t="s">
+        <v>407</v>
+      </c>
+      <c r="D31" t="s">
+        <v>253</v>
+      </c>
+      <c r="E31" t="s">
+        <v>408</v>
+      </c>
+      <c r="F31" t="s">
+        <v>409</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>411</v>
+      </c>
+      <c r="B32" t="s">
+        <v>412</v>
+      </c>
+      <c r="C32" t="s">
+        <v>413</v>
+      </c>
+      <c r="D32" t="s">
+        <v>253</v>
+      </c>
+      <c r="E32" t="s">
+        <v>414</v>
+      </c>
+      <c r="F32" t="s">
+        <v>415</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>417</v>
+      </c>
+      <c r="B33" t="s">
+        <v>412</v>
+      </c>
+      <c r="C33" t="s">
+        <v>418</v>
+      </c>
+      <c r="D33" t="s">
+        <v>253</v>
+      </c>
+      <c r="E33" t="s">
+        <v>419</v>
+      </c>
+      <c r="F33" t="s">
+        <v>415</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>417</v>
+      </c>
+      <c r="B34" t="s">
+        <v>412</v>
+      </c>
+      <c r="C34" t="s">
+        <v>421</v>
+      </c>
+      <c r="D34" t="s">
+        <v>253</v>
+      </c>
+      <c r="E34" t="s">
+        <v>422</v>
+      </c>
+      <c r="F34" t="s">
+        <v>415</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>424</v>
+      </c>
+      <c r="B35" t="s">
+        <v>425</v>
+      </c>
+      <c r="C35" t="s">
+        <v>426</v>
+      </c>
+      <c r="D35" t="s">
+        <v>285</v>
+      </c>
+      <c r="E35" t="s">
+        <v>396</v>
+      </c>
+      <c r="F35" t="s">
+        <v>427</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>429</v>
+      </c>
+      <c r="B36" t="s">
+        <v>430</v>
+      </c>
+      <c r="C36" t="s">
+        <v>431</v>
+      </c>
+      <c r="D36" t="s">
+        <v>265</v>
+      </c>
+      <c r="E36" t="s">
+        <v>432</v>
+      </c>
+      <c r="F36" t="s">
+        <v>433</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>435</v>
+      </c>
+      <c r="B37" t="s">
+        <v>436</v>
+      </c>
+      <c r="C37" t="s">
+        <v>437</v>
+      </c>
+      <c r="D37" t="s">
+        <v>265</v>
+      </c>
+      <c r="E37" t="s">
+        <v>438</v>
+      </c>
+      <c r="F37" t="s">
+        <v>439</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>441</v>
+      </c>
+      <c r="B38" t="s">
+        <v>406</v>
+      </c>
+      <c r="C38" t="s">
+        <v>407</v>
+      </c>
+      <c r="D38" t="s">
+        <v>253</v>
+      </c>
+      <c r="E38" t="s">
+        <v>408</v>
+      </c>
+      <c r="F38" t="s">
+        <v>409</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>443</v>
+      </c>
+      <c r="B39" t="s">
+        <v>444</v>
+      </c>
+      <c r="C39" t="s">
+        <v>445</v>
+      </c>
+      <c r="D39" t="s">
+        <v>246</v>
+      </c>
+      <c r="E39" t="s">
+        <v>446</v>
+      </c>
+      <c r="F39" t="s">
+        <v>447</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>449</v>
+      </c>
+      <c r="B40" t="s">
+        <v>292</v>
+      </c>
+      <c r="C40" t="s">
+        <v>293</v>
+      </c>
+      <c r="D40" t="s">
+        <v>253</v>
+      </c>
+      <c r="E40" t="s">
+        <v>294</v>
+      </c>
+      <c r="F40" t="s">
+        <v>295</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>451</v>
+      </c>
+      <c r="B41" t="s">
+        <v>425</v>
+      </c>
+      <c r="C41" t="s">
+        <v>452</v>
+      </c>
+      <c r="D41" t="s">
+        <v>253</v>
+      </c>
+      <c r="E41" t="s">
+        <v>453</v>
+      </c>
+      <c r="F41" t="s">
+        <v>427</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>455</v>
+      </c>
+      <c r="B42" t="s">
+        <v>456</v>
+      </c>
+      <c r="C42" t="s">
+        <v>176</v>
+      </c>
+      <c r="D42" t="s">
+        <v>253</v>
+      </c>
+      <c r="E42" t="s">
+        <v>457</v>
+      </c>
+      <c r="F42" t="s">
+        <v>458</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>460</v>
+      </c>
+      <c r="B43" t="s">
+        <v>412</v>
+      </c>
+      <c r="C43" t="s">
+        <v>461</v>
+      </c>
+      <c r="D43" t="s">
+        <v>253</v>
+      </c>
+      <c r="E43" t="s">
+        <v>408</v>
+      </c>
+      <c r="F43" t="s">
+        <v>415</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>463</v>
+      </c>
+      <c r="B44" t="s">
+        <v>383</v>
+      </c>
+      <c r="C44" t="s">
+        <v>384</v>
+      </c>
+      <c r="D44" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" t="s">
+        <v>464</v>
+      </c>
+      <c r="F44" t="s">
+        <v>386</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>466</v>
+      </c>
+      <c r="B45" t="s">
+        <v>467</v>
+      </c>
+      <c r="C45" t="s">
+        <v>468</v>
+      </c>
+      <c r="D45" t="s">
+        <v>253</v>
+      </c>
+      <c r="E45" t="s">
+        <v>469</v>
+      </c>
+      <c r="F45" t="s">
+        <v>375</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>471</v>
+      </c>
+      <c r="B46" t="s">
+        <v>472</v>
+      </c>
+      <c r="C46" t="s">
+        <v>357</v>
+      </c>
+      <c r="D46" t="s">
+        <v>253</v>
+      </c>
+      <c r="E46" t="s">
+        <v>380</v>
+      </c>
+      <c r="F46" t="s">
+        <v>473</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>471</v>
+      </c>
+      <c r="B47" t="s">
+        <v>475</v>
+      </c>
+      <c r="C47" t="s">
+        <v>476</v>
+      </c>
+      <c r="D47" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" t="s">
+        <v>247</v>
+      </c>
+      <c r="F47" t="s">
+        <v>477</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>479</v>
+      </c>
+      <c r="B48" t="s">
+        <v>383</v>
+      </c>
+      <c r="C48" t="s">
+        <v>384</v>
+      </c>
+      <c r="D48" t="s">
+        <v>253</v>
+      </c>
+      <c r="E48" t="s">
+        <v>385</v>
+      </c>
+      <c r="F48" t="s">
+        <v>386</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>481</v>
+      </c>
+      <c r="B49" t="s">
+        <v>482</v>
+      </c>
+      <c r="C49" t="s">
+        <v>384</v>
+      </c>
+      <c r="D49" t="s">
+        <v>253</v>
+      </c>
+      <c r="E49" t="s">
+        <v>464</v>
+      </c>
+      <c r="F49" t="s">
+        <v>483</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>485</v>
+      </c>
+      <c r="B50" t="s">
+        <v>486</v>
+      </c>
+      <c r="C50" t="s">
+        <v>487</v>
+      </c>
+      <c r="D50" t="s">
+        <v>253</v>
+      </c>
+      <c r="E50" t="s">
+        <v>488</v>
+      </c>
+      <c r="F50" t="s">
+        <v>489</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>491</v>
+      </c>
+      <c r="B51" t="s">
+        <v>492</v>
+      </c>
+      <c r="C51" t="s">
+        <v>431</v>
+      </c>
+      <c r="D51" t="s">
+        <v>253</v>
+      </c>
+      <c r="E51" t="s">
+        <v>493</v>
+      </c>
+      <c r="F51" t="s">
+        <v>494</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>496</v>
+      </c>
+      <c r="B52" t="s">
+        <v>497</v>
+      </c>
+      <c r="C52" t="s">
+        <v>384</v>
+      </c>
+      <c r="D52" t="s">
+        <v>253</v>
+      </c>
+      <c r="E52" t="s">
+        <v>498</v>
+      </c>
+      <c r="F52" t="s">
+        <v>247</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>500</v>
+      </c>
+      <c r="B53" t="s">
+        <v>501</v>
+      </c>
+      <c r="C53" t="s">
+        <v>335</v>
+      </c>
+      <c r="D53" t="s">
+        <v>253</v>
+      </c>
+      <c r="E53" t="s">
+        <v>502</v>
+      </c>
+      <c r="F53" t="s">
+        <v>503</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>505</v>
+      </c>
+      <c r="B54" t="s">
+        <v>506</v>
+      </c>
+      <c r="C54" t="s">
+        <v>507</v>
+      </c>
+      <c r="D54" t="s">
+        <v>253</v>
+      </c>
+      <c r="E54" t="s">
+        <v>247</v>
+      </c>
+      <c r="F54" t="s">
+        <v>508</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>510</v>
+      </c>
+      <c r="B55" t="s">
+        <v>511</v>
+      </c>
+      <c r="C55" t="s">
+        <v>323</v>
+      </c>
+      <c r="D55" t="s">
+        <v>253</v>
+      </c>
+      <c r="E55" t="s">
+        <v>254</v>
+      </c>
+      <c r="F55" t="s">
+        <v>512</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>514</v>
+      </c>
+      <c r="B56" t="s">
+        <v>511</v>
+      </c>
+      <c r="C56" t="s">
+        <v>323</v>
+      </c>
+      <c r="D56" t="s">
+        <v>253</v>
+      </c>
+      <c r="E56" t="s">
+        <v>247</v>
+      </c>
+      <c r="F56" t="s">
+        <v>512</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>516</v>
+      </c>
+      <c r="B57" t="s">
+        <v>501</v>
+      </c>
+      <c r="C57" t="s">
+        <v>335</v>
+      </c>
+      <c r="D57" t="s">
+        <v>253</v>
+      </c>
+      <c r="E57" t="s">
+        <v>517</v>
+      </c>
+      <c r="F57" t="s">
+        <v>503</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>519</v>
+      </c>
+      <c r="B58" t="s">
+        <v>520</v>
+      </c>
+      <c r="C58" t="s">
+        <v>38</v>
+      </c>
+      <c r="D58" t="s">
+        <v>253</v>
+      </c>
+      <c r="E58" t="s">
+        <v>521</v>
+      </c>
+      <c r="F58" t="s">
+        <v>522</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>524</v>
+      </c>
+      <c r="B59" t="s">
+        <v>475</v>
+      </c>
+      <c r="C59" t="s">
+        <v>476</v>
+      </c>
+      <c r="D59" t="s">
+        <v>253</v>
+      </c>
+      <c r="E59" t="s">
+        <v>247</v>
+      </c>
+      <c r="F59" t="s">
+        <v>477</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>526</v>
+      </c>
+      <c r="B60" t="s">
+        <v>425</v>
+      </c>
+      <c r="C60" t="s">
+        <v>527</v>
+      </c>
+      <c r="D60" t="s">
+        <v>285</v>
+      </c>
+      <c r="E60" t="s">
+        <v>396</v>
+      </c>
+      <c r="F60" t="s">
+        <v>427</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>529</v>
+      </c>
+      <c r="B61" t="s">
+        <v>530</v>
+      </c>
+      <c r="C61" t="s">
+        <v>452</v>
+      </c>
+      <c r="D61" t="s">
+        <v>265</v>
+      </c>
+      <c r="E61" t="s">
+        <v>531</v>
+      </c>
+      <c r="F61" t="s">
+        <v>532</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>534</v>
+      </c>
+      <c r="B62" t="s">
+        <v>535</v>
+      </c>
+      <c r="C62" t="s">
+        <v>384</v>
+      </c>
+      <c r="D62" t="s">
+        <v>253</v>
+      </c>
+      <c r="E62" t="s">
+        <v>536</v>
+      </c>
+      <c r="F62" t="s">
+        <v>537</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>539</v>
+      </c>
+      <c r="B63" t="s">
+        <v>540</v>
+      </c>
+      <c r="C63" t="s">
+        <v>357</v>
+      </c>
+      <c r="D63" t="s">
+        <v>253</v>
+      </c>
+      <c r="E63" t="s">
+        <v>247</v>
+      </c>
+      <c r="F63" t="s">
+        <v>267</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>542</v>
+      </c>
+      <c r="B64" t="s">
+        <v>543</v>
+      </c>
+      <c r="C64" t="s">
+        <v>323</v>
+      </c>
+      <c r="D64" t="s">
+        <v>253</v>
+      </c>
+      <c r="E64" t="s">
+        <v>544</v>
+      </c>
+      <c r="F64" t="s">
+        <v>545</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>547</v>
+      </c>
+      <c r="B65" t="s">
+        <v>548</v>
+      </c>
+      <c r="C65" t="s">
+        <v>452</v>
+      </c>
+      <c r="D65" t="s">
+        <v>253</v>
+      </c>
+      <c r="E65" t="s">
+        <v>549</v>
+      </c>
+      <c r="F65" t="s">
+        <v>550</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>552</v>
+      </c>
+      <c r="B66" t="s">
+        <v>383</v>
+      </c>
+      <c r="C66" t="s">
+        <v>384</v>
+      </c>
+      <c r="D66" t="s">
+        <v>253</v>
+      </c>
+      <c r="E66" t="s">
+        <v>553</v>
+      </c>
+      <c r="F66" t="s">
+        <v>554</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>556</v>
+      </c>
+      <c r="B67" t="s">
+        <v>557</v>
+      </c>
+      <c r="C67" t="s">
+        <v>558</v>
+      </c>
+      <c r="D67" t="s">
+        <v>285</v>
+      </c>
+      <c r="E67" t="s">
+        <v>396</v>
+      </c>
+      <c r="F67" t="s">
+        <v>559</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>561</v>
+      </c>
+      <c r="B68" t="s">
+        <v>562</v>
+      </c>
+      <c r="C68" t="s">
+        <v>384</v>
+      </c>
+      <c r="D68" t="s">
+        <v>253</v>
+      </c>
+      <c r="E68" t="s">
+        <v>380</v>
+      </c>
+      <c r="F68" t="s">
+        <v>563</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>565</v>
+      </c>
+      <c r="B69" t="s">
+        <v>566</v>
+      </c>
+      <c r="C69" t="s">
+        <v>567</v>
+      </c>
+      <c r="D69" t="s">
+        <v>253</v>
+      </c>
+      <c r="E69" t="s">
+        <v>536</v>
+      </c>
+      <c r="F69" t="s">
+        <v>568</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>570</v>
+      </c>
+      <c r="B70" t="s">
+        <v>571</v>
+      </c>
+      <c r="C70" t="s">
+        <v>452</v>
+      </c>
+      <c r="D70" t="s">
+        <v>253</v>
+      </c>
+      <c r="E70" t="s">
+        <v>572</v>
+      </c>
+      <c r="F70" t="s">
+        <v>573</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>575</v>
+      </c>
+      <c r="B71" t="s">
+        <v>576</v>
+      </c>
+      <c r="C71" t="s">
+        <v>357</v>
+      </c>
+      <c r="D71" t="s">
+        <v>253</v>
+      </c>
+      <c r="E71" t="s">
+        <v>577</v>
+      </c>
+      <c r="F71" t="s">
+        <v>578</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>580</v>
+      </c>
+      <c r="B72" t="s">
+        <v>581</v>
+      </c>
+      <c r="C72" t="s">
+        <v>582</v>
+      </c>
+      <c r="D72" t="s">
+        <v>253</v>
+      </c>
+      <c r="E72" t="s">
+        <v>583</v>
+      </c>
+      <c r="F72" t="s">
+        <v>584</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>586</v>
+      </c>
+      <c r="B73" t="s">
+        <v>587</v>
+      </c>
+      <c r="C73" t="s">
+        <v>588</v>
+      </c>
+      <c r="D73" t="s">
+        <v>253</v>
+      </c>
+      <c r="E73" t="s">
+        <v>589</v>
+      </c>
+      <c r="F73" t="s">
+        <v>590</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>592</v>
+      </c>
+      <c r="B74" t="s">
+        <v>593</v>
+      </c>
+      <c r="C74" t="s">
+        <v>277</v>
+      </c>
+      <c r="D74" t="s">
+        <v>253</v>
+      </c>
+      <c r="E74" t="s">
+        <v>594</v>
+      </c>
+      <c r="F74" t="s">
+        <v>595</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>597</v>
+      </c>
+      <c r="B75" t="s">
+        <v>598</v>
+      </c>
+      <c r="C75" t="s">
+        <v>357</v>
+      </c>
+      <c r="D75" t="s">
+        <v>246</v>
+      </c>
+      <c r="E75" t="s">
+        <v>247</v>
+      </c>
+      <c r="F75" t="s">
+        <v>599</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>601</v>
+      </c>
+      <c r="B76" t="s">
+        <v>602</v>
+      </c>
+      <c r="C76" t="s">
+        <v>335</v>
+      </c>
+      <c r="D76" t="s">
+        <v>253</v>
+      </c>
+      <c r="E76" t="s">
+        <v>603</v>
+      </c>
+      <c r="F76" t="s">
+        <v>604</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>606</v>
+      </c>
+      <c r="B77" t="s">
+        <v>607</v>
+      </c>
+      <c r="C77" t="s">
+        <v>608</v>
+      </c>
+      <c r="D77" t="s">
+        <v>253</v>
+      </c>
+      <c r="E77" t="s">
+        <v>609</v>
+      </c>
+      <c r="F77" t="s">
+        <v>610</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>612</v>
+      </c>
+      <c r="B78" t="s">
+        <v>613</v>
+      </c>
+      <c r="C78" t="s">
+        <v>614</v>
+      </c>
+      <c r="D78" t="s">
+        <v>265</v>
+      </c>
+      <c r="E78" t="s">
+        <v>615</v>
+      </c>
+      <c r="F78" t="s">
+        <v>247</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>617</v>
+      </c>
+      <c r="B79" t="s">
+        <v>618</v>
+      </c>
+      <c r="C79" t="s">
+        <v>619</v>
+      </c>
+      <c r="D79" t="s">
+        <v>278</v>
+      </c>
+      <c r="E79" t="s">
+        <v>620</v>
+      </c>
+      <c r="F79" t="s">
+        <v>621</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>623</v>
+      </c>
+      <c r="B80" t="s">
+        <v>283</v>
+      </c>
+      <c r="C80" t="s">
+        <v>284</v>
+      </c>
+      <c r="D80" t="s">
+        <v>285</v>
+      </c>
+      <c r="E80" t="s">
+        <v>247</v>
+      </c>
+      <c r="F80" t="s">
+        <v>289</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>625</v>
+      </c>
+      <c r="B81" t="s">
+        <v>283</v>
+      </c>
+      <c r="C81" t="s">
+        <v>626</v>
+      </c>
+      <c r="D81" t="s">
+        <v>285</v>
+      </c>
+      <c r="E81" t="s">
+        <v>247</v>
+      </c>
+      <c r="F81" t="s">
+        <v>627</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-09.xlsx
+++ b/docs/xlsx/jobs-2026-09-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="932">
   <si>
     <t>Title</t>
   </si>
@@ -745,6 +745,24 @@
     <t>https://www.conservationjobboard.com/job-listing-year-round-field-crew-member-virginia-roanoke-virginia/4905956714</t>
   </si>
   <si>
+    <t>Open Space Technician</t>
+  </si>
+  <si>
+    <t>Cupertino, California, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/open-space-technician-3/</t>
+  </si>
+  <si>
     <t>🌍 Líder de Equipo F2F | Donantes Individuales | Turno Mañana o Tarde | CABA</t>
   </si>
   <si>
@@ -802,6 +820,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/f36cdd16b0ef4f79be1581ece36bc7fd-administrative-assistant-membership-audience-services-maine-public-broadcasting-portland</t>
   </si>
   <si>
+    <t>Advocacy &amp; Leadership Program Coordinator</t>
+  </si>
+  <si>
+    <t>Uri L'Tzedek</t>
+  </si>
+  <si>
+    <t>Remote (District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Civic Engagement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2977d2488b5b4114877c728bee02b5c9-advocacy-leadership-program-coordinator-uri-ltzedek-scottsdale</t>
+  </si>
+  <si>
+    <t>Afterschool Teacher and Teacher Assistants</t>
+  </si>
+  <si>
+    <t>Operation Shoestring</t>
+  </si>
+  <si>
+    <t>Jackson, Mississippi</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4f15396adcc43df99ee89cdc8cac8c7-afterschool-teacher-and-teacher-assistants-operation-shoestring-jackson</t>
+  </si>
+  <si>
     <t>ASESOR(A) EDUCADOR(A) COMINUTARIO(A)</t>
   </si>
   <si>
@@ -823,6 +880,105 @@
     <t>https://www.idealist.org/en/nonprofit-job/f98bdfb1d2a246859a9dc99f135fcab1-asesora-educadora-cominutarioa-medicos-sin-fronteras-en-mexico-ac-chilpancingo-de-los-bravo</t>
   </si>
   <si>
+    <t>Assistant Director of Advancement Services</t>
+  </si>
+  <si>
+    <t>Mount Saint Mary College</t>
+  </si>
+  <si>
+    <t>Newburgh, New York</t>
+  </si>
+  <si>
+    <t>USD 62353.20 - 62353.20/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce73a8ecfcfe4b44b4c0a3354d4e8467-assistant-director-of-advancement-services-mount-saint-mary-college-newburgh</t>
+  </si>
+  <si>
+    <t>Assistant Director of Development</t>
+  </si>
+  <si>
+    <t>Essex County Greenbelt Association</t>
+  </si>
+  <si>
+    <t>Essex, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Urban Areas, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e16b845884a48faa998e20d5a78c92e-assistant-director-of-development-essex-county-greenbelt-association-essex</t>
+  </si>
+  <si>
+    <t>Assistant, Associate, or Full Professor of Law</t>
+  </si>
+  <si>
+    <t>City University of New York (CUNY) School of Law</t>
+  </si>
+  <si>
+    <t>Queens, New York</t>
+  </si>
+  <si>
+    <t>USD 126394.00 - 136606.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc42997a4ef64f7eb36f175c63063665-assistant-associate-or-full-professor-of-law-city-university-of-new-york-cuny-school-of-law-queens</t>
+  </si>
+  <si>
+    <t>Associate - Talent, Finance, and Operations (TFO)</t>
+  </si>
+  <si>
+    <t>Vote Solar</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 35.77 - 38.80/hour</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1807a774cdbc440d91c60a00407dbf7e-associate-talent-finance-and-operations-tfo-vote-solar-oakland</t>
+  </si>
+  <si>
+    <t>Associate Attorney</t>
+  </si>
+  <si>
+    <t>Aqua Terra Aeris Law Group</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/55e5eb66abf54b97a108118eb6c0dc15-associate-attorney-aqua-terra-aeris-law-group-oakland</t>
+  </si>
+  <si>
+    <t>BARBERO PARA TALLERES CON JOVENES</t>
+  </si>
+  <si>
+    <t>Centros Barriales - Municipalidad de Vicente López</t>
+  </si>
+  <si>
+    <t>Vicente López, Colima, MX</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/0292a89dc0984f418c42da6fb1ebc48d-barbero-para-talleres-con-jovenes-centros-barriales-municipalidad-de-vicente-lopez-vicente-lopez</t>
+  </si>
+  <si>
     <t>Bilingual Legal Advocate</t>
   </si>
   <si>
@@ -841,6 +997,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/74dc1f460d7942448ed4755df8049f3d-bilingual-legal-advocate-sexual-assault-legal-institute-silver-spring</t>
   </si>
   <si>
+    <t>Business Development &amp; Project Manager</t>
+  </si>
+  <si>
+    <t>Pyramid Communications</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 66800.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/d9e0186936ed44fb81e7dd59f4ec5e1d-business-development-project-manager-pyramid-communications-seattle</t>
+  </si>
+  <si>
     <t>Canvasser - CA Calls Yes on 3, No on 39</t>
   </si>
   <si>
@@ -871,9 +1045,6 @@
     <t>Córdoba, Córdoba, AR</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>Community Development, Children Youth</t>
   </si>
   <si>
@@ -907,6 +1078,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/b1748108dc9640808684e7d06a952e4b-case-manager-proactive-community-services-flossmoor</t>
   </si>
   <si>
+    <t>Case-Handling Paralegal, Housing Unit, CAMBA Legal Services</t>
+  </si>
+  <si>
+    <t>CAMBA</t>
+  </si>
+  <si>
+    <t>USD 63860.00 - 96551.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55a0235bdb95495da34f3de88445bd2e-case-handling-paralegal-housing-unit-camba-legal-services-camba-kings-county</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer (CEO)</t>
+  </si>
+  <si>
+    <t>Mainstream Nonprofit Solutions</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>Children Youth, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a8e8846d5f3455db348d579113207e2-chief-executive-officer-ceo-mainstream-nonprofit-solutions-dallas</t>
+  </si>
+  <si>
+    <t>Topeka, Kansas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f5ba6659f914887b9514959a1a36742-chief-executive-officer-ceo-mainstream-nonprofit-solutions-topeka</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>Yellowstone Boys &amp; Girls Ranch</t>
+  </si>
+  <si>
+    <t>Billings, Montana</t>
+  </si>
+  <si>
+    <t>USD 132079.74 - 148656.82/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d511896d95f84a79845bd1941a80f4fc-chief-financial-officer-yellowstone-boys-girls-ranch-billings</t>
+  </si>
+  <si>
     <t>Chief, Community Leadership &amp; Training Institute</t>
   </si>
   <si>
@@ -925,6 +1150,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/cdb4b9fa5c8d4660a66ca6baf0f13f66-chief-community-leadership-training-institute-nyc-kids-rise-long-island-city</t>
   </si>
   <si>
+    <t>Climate &amp; Energy Attorney (Connecticut)</t>
+  </si>
+  <si>
+    <t>The Conservation Law Foundation</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5f1ef18a0cc473c886aeee8eefa9433-climate-energy-attorney-connecticut-the-conservation-law-foundation-new-haven</t>
+  </si>
+  <si>
+    <t>Communications Associate – Media, Content &amp; Campaigns</t>
+  </si>
+  <si>
+    <t>Hispanic Access Foundation</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3cbc5a8901714e6db8ef7a41a9d70a8f-communications-associate-media-content-campaigns-hispanic-access-foundation-washington</t>
+  </si>
+  <si>
+    <t>Communications Manager, West (Remote - Western US)</t>
+  </si>
+  <si>
+    <t>USD 89900.00 - 97500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0afefd6178c74af79d15b2d39d39c30b-communications-manager-west-remote-western-us-vote-solar-oakland</t>
+  </si>
+  <si>
     <t>Community Engagement Director</t>
   </si>
   <si>
@@ -943,6 +1204,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/805da3f3ee51434eb2ab357aa21f7e53-community-engagement-director-maine-equal-justice-augusta</t>
   </si>
   <si>
+    <t>Community Manager</t>
+  </si>
+  <si>
+    <t>Diabetes Foundation</t>
+  </si>
+  <si>
+    <t>Mahwah, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61abcc12a09e4885825b5701c3c346e6-community-manager-diabetes-foundation-mahwah</t>
+  </si>
+  <si>
+    <t>Community Organizer - Eastern, SD</t>
+  </si>
+  <si>
+    <t>Dakota Rural Action</t>
+  </si>
+  <si>
+    <t>Sioux Falls, South Dakota</t>
+  </si>
+  <si>
+    <t>USD 50000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b63954a81914ccca387925e71e14c56-community-organizer-eastern-sd-dakota-rural-action-sioux-falls</t>
+  </si>
+  <si>
     <t>Community Resource Navigator</t>
   </si>
   <si>
@@ -1015,6 +1312,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/eb2790ea40a041718acd1530c8f1e11e-creative-digital-content-strategist-advancement-project-washington</t>
   </si>
   <si>
+    <t>Crisis Intervention Specialist - Oakland</t>
+  </si>
+  <si>
+    <t>Family Violence Law Center</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>USD 36.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>Women, Victim Support, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b2046744d9d54b81b96d6d7c91739338-crisis-intervention-specialist-oakland-family-violence-law-center-oakland</t>
+  </si>
+  <si>
     <t>Data Collector</t>
   </si>
   <si>
@@ -1033,6 +1348,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/a833caba93914482ac1bdcaa3f5cc158-data-collector-harvard-th-chan-school-of-public-health-boston</t>
   </si>
   <si>
+    <t>Dean of Students</t>
+  </si>
+  <si>
+    <t>Arts for Learning Maryland</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90fabbc0f5ba4fa18068005ad79c6f68-dean-of-students-arts-for-learning-maryland-baltimore</t>
+  </si>
+  <si>
     <t>Deputy Director of Government Affairs - Hybrid Sacramento CA</t>
   </si>
   <si>
@@ -1063,6 +1393,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/6177120f36154f3982af8cac86124ef8-development-manager-marin-county-bicycle-coalition-fairfax</t>
   </si>
   <si>
+    <t>Development Officer</t>
+  </si>
+  <si>
+    <t>Tacoma Rescue Mission</t>
+  </si>
+  <si>
+    <t>Tacoma, Washington</t>
+  </si>
+  <si>
+    <t>USD 37.05 - 44.94/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a281f558ae5145619a359aa95fbb9b56-development-officer-tacoma-rescue-mission-tacoma</t>
+  </si>
+  <si>
     <t>DEVELOPMENT OPERATIONS MANAGER</t>
   </si>
   <si>
@@ -1087,24 +1435,36 @@
     <t>iMission Institute</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 45.00/hour</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/consultant-job/1a9be73ba23c4777a006e0949fcd3420-digital-marketing-funrdraising-consultant-imission-institute-new-haven</t>
   </si>
   <si>
+    <t>Director of Business Administration</t>
+  </si>
+  <si>
+    <t>Eliot Unitarian Universalist Chapel</t>
+  </si>
+  <si>
+    <t>Kirkwood, Missouri</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/477bdb8f7e024a66b530743de2908497-director-of-business-administration-eliot-unitarian-universalist-chapel-kirkwood</t>
+  </si>
+  <si>
     <t>Director of Development</t>
   </si>
   <si>
     <t>Maryland Center on Economic Policy</t>
   </si>
   <si>
-    <t>Baltimore, Maryland</t>
-  </si>
-  <si>
     <t>USD 70000.00 - 90000.00/year</t>
   </si>
   <si>
@@ -1114,6 +1474,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/a660a47130564c138b6186854df6bb3a-director-of-development-maryland-center-on-economic-policy-baltimore</t>
   </si>
   <si>
+    <t>Director of Finance - Remote</t>
+  </si>
+  <si>
+    <t>Insperity-Client</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/f94874c2fb20470fb46192f532e2b0e1-director-of-finance-remote-insperity-client-kingwood</t>
+  </si>
+  <si>
+    <t>Director of Immigrant Rights Policy</t>
+  </si>
+  <si>
+    <t>The New York Immigration Coalition</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 98400.00 - 98400.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43656feaf4294a8a8dfad303b319e829-director-of-immigrant-rights-policy-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Director of Institutional Giving</t>
+  </si>
+  <si>
+    <t>Shalom Hartman Institute</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1b8a128970d548968c57575c5b02759d-director-of-institutional-giving-shalom-hartman-institute-new-york</t>
+  </si>
+  <si>
+    <t>Director of Policy</t>
+  </si>
+  <si>
+    <t>Project On Government Oversight</t>
+  </si>
+  <si>
+    <t>USD 128000.00 - 144000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/818681ef86a84bdd906f7065a11dcd88-director-of-policy-project-on-government-oversight-washington</t>
+  </si>
+  <si>
     <t>Director of Programs</t>
   </si>
   <si>
@@ -1162,15 +1582,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/0e9aa17c4de54494a593237a1e2408b3-director-do-what-you-love-alzheimers-association-massachusetts-new-hampshire-chapter-san-jose</t>
   </si>
   <si>
+    <t>Director, Editorial &amp; Media Relations</t>
+  </si>
+  <si>
+    <t>Inflection Point Agency</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/e8293f4a7bdf481095f0400a25802258-director-editorial-media-relations-inflection-point-agency-niwot</t>
+  </si>
+  <si>
+    <t>Director, Health Information Technology</t>
+  </si>
+  <si>
+    <t>Coalition of Orange County Community Health Centers</t>
+  </si>
+  <si>
+    <t>Orange, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae7e189f234a45668ac6ed743c6b81bd-director-health-information-technology-coalition-of-orange-county-community-health-centers-orange</t>
+  </si>
+  <si>
     <t>Director, Technology &amp; Information Systems</t>
   </si>
   <si>
     <t>The Breast Cancer Research Foundation</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 175000.00 - 190000.00/year</t>
   </si>
   <si>
@@ -1180,6 +1627,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/960e6ab7755c472db688f2abbbde0291-director-technology-information-systems-the-breast-cancer-research-foundation-new-york</t>
   </si>
   <si>
+    <t>Disability Peer Advocate Bilingual/Spanish</t>
+  </si>
+  <si>
+    <t>Boston Center for Independent Living, Inc.</t>
+  </si>
+  <si>
+    <t>USD 45500.00 - 45500.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58fa1ec9f40a4f54a25c30defac5d75d-disability-peer-advocate-bilingualspanish-boston-center-for-independent-living-inc-boston</t>
+  </si>
+  <si>
     <t>Disbursement Associate</t>
   </si>
   <si>
@@ -1195,6 +1657,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/903c324d136042e4821a0bbc29e60627-disbursement-associate-the-ford-foundation-new-york</t>
   </si>
   <si>
+    <t>Education and Committee Coordinator (Part-time, hybrid)</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Environment, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/542fdfaf26444f2f891a08536b71da98-education-and-committee-coordinator-part-time-hybrid-the-choice-inc-washington</t>
+  </si>
+  <si>
     <t>Education Coordinator</t>
   </si>
   <si>
@@ -1225,12 +1702,24 @@
     <t>USD 140000.00 - 170000.00/year</t>
   </si>
   <si>
-    <t>Housing Homelessness</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5491bacbc48a4f609796d0371b2624c2-executive-director-lake-city-partners-ending-homelessness-shoreline</t>
   </si>
   <si>
+    <t>Christian Camp Meeting Association</t>
+  </si>
+  <si>
+    <t>Barnstable, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Sports Recreation, Travel Hospitality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be4e888465f7452daed0984ebd4319e7-executive-director-christian-camp-meeting-association-barnstable</t>
+  </si>
+  <si>
     <t>Family Advocacy Unit Staff Attorney</t>
   </si>
   <si>
@@ -1261,9 +1750,6 @@
     <t>USD 80000.00 - 93000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Family, Mental Health</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/001a81e1aba34a9ea699a91a246cad27-family-intervention-specialist-in-home-family-therapy-youth-villages-pittsfield</t>
   </si>
   <si>
@@ -1303,6 +1789,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/1b1dffa1869548a2b1814f3bfec81aef-family-literacy-program-coordinator-illinois-workers-in-action-bolingbrook</t>
   </si>
   <si>
+    <t>Family Resident Services Coordinator</t>
+  </si>
+  <si>
+    <t>Innovative Housing, Inc.</t>
+  </si>
+  <si>
+    <t>Lincoln City, Oregon</t>
+  </si>
+  <si>
+    <t>USD 44000.00 - 44000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40f0f21876984d2088ff7eb49aa907f7-family-resident-services-coordinator-innovative-housing-inc-lincoln-city</t>
+  </si>
+  <si>
     <t>Florida Early Learning Tutor</t>
   </si>
   <si>
@@ -1321,6 +1825,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/6209bea99e7e4400b7e5fe7f85b89be7-florida-early-learning-tutor-ampact-miami</t>
   </si>
   <si>
+    <t>Fundraising &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>10,000 Friends of Pennsylvania</t>
+  </si>
+  <si>
+    <t>Remote (Pennsylvania)</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87c45949ff1d492a9acd3fa7cb1a3add-fundraising-communications-manager-10000-friends-of-pennsylvania-harrisburg</t>
+  </si>
+  <si>
+    <t>Garden Project Specialist</t>
+  </si>
+  <si>
+    <t>Portland Japanese Garden</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f0a4ad3a466483bbfe66c1a5c807b36-garden-project-specialist-portland-japanese-garden-portland</t>
+  </si>
+  <si>
     <t>Head of Mission - Syria</t>
   </si>
   <si>
@@ -1453,6 +1993,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/ff87aa5465c24058938ae47426b3ef94-major-gifts-officer-american-indian-college-fund-denver</t>
   </si>
   <si>
+    <t>New York Civil Liberties Union Foundation</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/d19980f185904efaa36dfb5d99bc9586-major-gifts-officer-new-york-civil-liberties-union-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Manager of Sales Development</t>
+  </si>
+  <si>
+    <t>OnYourMark Education</t>
+  </si>
+  <si>
+    <t>USD 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38701e1baa0b4f50992cfb209acd7c05-manager-of-sales-development-onyourmark-education-los-angeles</t>
+  </si>
+  <si>
+    <t>Managing Director</t>
+  </si>
+  <si>
+    <t>A Growing Culture</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b2c9b04d4cb442897d3d166947f5a76-managing-director-a-growing-culture-asheville</t>
+  </si>
+  <si>
     <t>Managing Director, Gift Planning (Legacy Giving)</t>
   </si>
   <si>
@@ -1504,6 +2083,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/55159f32fd6944e6acfb6f6f4696af3e-nonprofit-fundraising-manager-achieve-miami-inc-miami</t>
   </si>
   <si>
+    <t>Office Coordinator</t>
+  </si>
+  <si>
+    <t>Eastside Village</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad2f7b2850734226828aacfc788b1d0e-office-coordinator-eastside-village-portland</t>
+  </si>
+  <si>
+    <t>Operations Assistant</t>
+  </si>
+  <si>
+    <t>Rainier Valley Food Bank</t>
+  </si>
+  <si>
+    <t>USD 32.70 - 32.70/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1b21d02b9d84c0499c8647c8cb9043c-operations-assistant-rainier-valley-food-bank-seattle</t>
+  </si>
+  <si>
     <t>Operations Coordinator - Genetics &amp; Genomics Research Labs</t>
   </si>
   <si>
@@ -1516,6 +2125,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/108217d2fc134a4498403cd36b413e24-operations-coordinator-genetics-genomics-research-labs-icahn-school-of-medicine-at-mount-sinai-department-of-genetics-and-genomic-sciences-new-york</t>
   </si>
   <si>
+    <t>Part-Time Group Leader (After-school Program)</t>
+  </si>
+  <si>
+    <t>"I Have A Dream" Foundation</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 19.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2cba69aae7f4a8aa5c23db94961501b-part-time-group-leader-after-school-program-i-have-a-dream-foundation-new-york</t>
+  </si>
+  <si>
     <t>Principal Health Inspector</t>
   </si>
   <si>
@@ -1546,6 +2170,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/37577aca593546c9b5701f26d9906786-profesional-en-derecho-ambiental-y-calidad-del-aire-peru-interamerican-association-for-environmental-defense-aida-ciudad-de-mexico</t>
   </si>
   <si>
+    <t>PROFESOR DE MATEMATICAS</t>
+  </si>
+  <si>
+    <t>Vicente López, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/64321be49de3467dba49f6acc9ffd71d-profesor-de-matematicas-centros-barriales-municipalidad-de-vicente-lopez-vicente-lopez</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/96166bb364ae4f8689ed50a6c41f67b7-profesor-de-matematicas-centros-barriales-municipalidad-de-vicente-lopez-vicente-lopez</t>
+  </si>
+  <si>
     <t>Program Coordinator (APT)</t>
   </si>
   <si>
@@ -1564,6 +2200,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/65e63360288f4d8cb8cf6a095635ea31-program-coordinator-ols-american-association-of-colleges-and-universities-washington</t>
   </si>
   <si>
+    <t>Program Coordinator or Program Assistant (Connecticut)</t>
+  </si>
+  <si>
+    <t>Community Development, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8752e05ebc5f46a5a264cf28a3e36f31-program-coordinator-or-program-assistant-connecticut-the-conservation-law-foundation-new-haven</t>
+  </si>
+  <si>
+    <t>Program Delivery Coordinator</t>
+  </si>
+  <si>
+    <t>HandsOn Bay Area</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 26.44 - 27.41/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53db0d82eb25447bacdbc326064006a3-program-delivery-coordinator-handson-bay-area-san-francisco</t>
+  </si>
+  <si>
     <t>Program Director - Entre Familia</t>
   </si>
   <si>
@@ -1588,6 +2251,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/de0e254d6ac74aad9670ceb83163345c-program-manager-jewish-community-center-sonoma-county-santa-rosa</t>
   </si>
   <si>
+    <t>Program Manager - Staten Island Advocacy Program</t>
+  </si>
+  <si>
+    <t>Baltic Street Wellness Solutions</t>
+  </si>
+  <si>
+    <t>Richmond County, New York</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd07ef33227c44d1afd6e9f8614d6f36-program-manager-staten-island-advocacy-program-baltic-street-wellness-solutions-richmond-county</t>
+  </si>
+  <si>
     <t>Program Officer</t>
   </si>
   <si>
@@ -1618,6 +2299,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/2a78bd698ac540e789721a3a12fa2a2d-project-assistant-social-services-job-training-program-chicago-il-region-temporary-hunger-free-america-chicago</t>
   </si>
   <si>
+    <t>Project Manager, Policy &amp; Government Affairs</t>
+  </si>
+  <si>
+    <t>USD 25.45 - 40.87/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/207b0c8686ba4eb8802748886b698e82-project-manager-policy-government-affairs-coalition-of-orange-county-community-health-centers-orange</t>
+  </si>
+  <si>
+    <t>Regional Head (Francophone Africa)</t>
+  </si>
+  <si>
+    <t>Lead Exposure Elimination Project</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a3da673f3d440a19cb9c660e5c0af5d-regional-head-francophone-africa-lead-exposure-elimination-project-london</t>
+  </si>
+  <si>
+    <t>Remote Volunteer Grant Writer - Global Health &amp; Education</t>
+  </si>
+  <si>
+    <t>HERF - HEALTH EDUCATION RECTITUDE FOUNDATION</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f2ef728b3494fbdaf2360804bbcfb0c-remote-volunteer-grant-writer-global-health-education-herf-health-education-rectitude-foundation-kampala</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73577b2436f0424487164c56d349c6e5-remote-volunteer-grant-writer-global-health-education-herf-health-education-rectitude-foundation-kampala</t>
+  </si>
+  <si>
     <t>Revenue Operations Coordinator</t>
   </si>
   <si>
@@ -1648,15 +2362,24 @@
     <t>National Parks Conservation Association</t>
   </si>
   <si>
-    <t>USD 55000.00 - 65000.00/year</t>
-  </si>
-  <si>
     <t>Environment</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/c6beb0a362954e1eae1bbcae133ca839-senior-development-coordinator-national-parks-conservation-association-washington</t>
   </si>
   <si>
+    <t>Senior Director, Client Financial Services (FP&amp;A)</t>
+  </si>
+  <si>
+    <t>Sunflower Services, PBC</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/7d6a9b553d244f88b44511abe05e40c7-senior-director-client-financial-services-fpa-sunflower-services-pbc-washington</t>
+  </si>
+  <si>
     <t>Senior Executive Assistant</t>
   </si>
   <si>
@@ -1672,6 +2395,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/7e468fa527304eedbbab36f864505216-senior-executive-assistant-interfaith-america-chicago</t>
   </si>
   <si>
+    <t>Senior Innovation Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f68515b5261947f29f60c980aafee658-senior-innovation-manager-lead-exposure-elimination-project-london</t>
+  </si>
+  <si>
+    <t>Senior Peer Specialist - Community Links</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61b84d107b2c447a9303e8802fa179b1-senior-peer-specialist-community-links-baltic-street-wellness-solutions-kings-county</t>
+  </si>
+  <si>
     <t>Senior Philanthropy Officer (Major Gifts Officer)</t>
   </si>
   <si>
@@ -1717,24 +2458,33 @@
     <t>Catlin Gabel School</t>
   </si>
   <si>
-    <t>Portland, Oregon</t>
-  </si>
-  <si>
     <t>Education, Children Youth</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/c59ae1d09d944aa582bf87876ee1c471-special-gifts-officer-catlin-gabel-school-portland</t>
   </si>
   <si>
+    <t>Sr. Regional Director, California (Remote- California)</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 122745.00 - 128730.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/357da5b4281d4cb099beca4b8895f4f7-sr-regional-director-california-remote-california-vote-solar-oakland</t>
+  </si>
+  <si>
     <t>Staff Accountant</t>
   </si>
   <si>
     <t>Chicago Lawyers' Committee For Civil Rights Under Law, Inc.</t>
   </si>
   <si>
-    <t>USD 60000.00 - 75000.00/year</t>
-  </si>
-  <si>
     <t>Economic Development, Legal Assistance, Race Ethnicity</t>
   </si>
   <si>
@@ -1756,6 +2506,84 @@
     <t>https://www.idealist.org/en/nonprofit-job/62783c67e562449a9babe9da8fa75540-staff-accountant-grants-and-compliance-everyone-on-los-angeles</t>
   </si>
   <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Leadership Counsel for Justice and Accountability</t>
+  </si>
+  <si>
+    <t>Fresno, California</t>
+  </si>
+  <si>
+    <t>USD 77500.00 - 92500.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/583c15cf05f745e1b85b236780fcd485-staff-attorney-leadership-counsel-for-justice-and-accountability-fresno</t>
+  </si>
+  <si>
+    <t>Coachella, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45f4fbb9711a4f708d9725092d04ba5a-staff-attorney-leadership-counsel-for-justice-and-accountability-coachella</t>
+  </si>
+  <si>
+    <t>New Jersey Consortium for Immigrant Children</t>
+  </si>
+  <si>
+    <t>Jersey City, New Jersey</t>
+  </si>
+  <si>
+    <t>Children Youth, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/31b415664e894f9cb86a982abc868a95-staff-attorney-new-jersey-consortium-for-immigrant-children-jersey-city</t>
+  </si>
+  <si>
+    <t>Immigration Center for Women and Children</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6aff8461e0364496a4b75d8926ace977-staff-attorney-immigration-center-for-women-and-children-san-francisco</t>
+  </si>
+  <si>
+    <t>Texas RioGrande Legal Aid, Inc. (TRLA)</t>
+  </si>
+  <si>
+    <t>Brownsville, Texas</t>
+  </si>
+  <si>
+    <t>USD 66929.00 - 91067.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd50cd59120c4a3e88dd05d79cfdaa9d-staff-attorney-texas-riogrande-legal-aid-inc-trla-brownsville</t>
+  </si>
+  <si>
+    <t>Del Rio, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cce06e6ecdbf4654951e1b3b8ca74936-staff-attorney-texas-riogrande-legal-aid-inc-trla-del-rio</t>
+  </si>
+  <si>
+    <t>Laredo, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbd8214c395c49c09e4dc3a5e7e97dba-staff-attorney-texas-riogrande-legal-aid-inc-trla-laredo</t>
+  </si>
+  <si>
+    <t>Corpus Christi, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1fe5311f4925406c913d541ba79d3023-staff-attorney-texas-riogrande-legal-aid-inc-trla-corpus-christi</t>
+  </si>
+  <si>
     <t>Staff Attorney, Family Defense, Queens</t>
   </si>
   <si>
@@ -1783,21 +2611,24 @@
     <t>Chicago, IL</t>
   </si>
   <si>
-    <t>USD 50000.00/year</t>
-  </si>
-  <si>
-    <t>Arts Music, Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/c09219377dee45be87fcf421c6b1444c-strings-orchestra-program-manager-merit-school-of-music-chicago</t>
   </si>
   <si>
+    <t>Sunday School Director - part time</t>
+  </si>
+  <si>
+    <t>Wilmington United Methodist Church</t>
+  </si>
+  <si>
+    <t>Wilmington, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0e5111720e940fb914ce21a9e1a8ebe-sunday-school-director-part-time-wilmington-united-methodist-church-wilmington</t>
+  </si>
+  <si>
     <t>Supervising Attorney</t>
   </si>
   <si>
-    <t>Immigration Center for Women and Children</t>
-  </si>
-  <si>
     <t>USD 95000.00 - 120000.00/year</t>
   </si>
   <si>
@@ -1807,6 +2638,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/26dc0502e3e64754b51b0710f78e132b-supervising-attorney-immigration-center-for-women-and-children-los-angeles</t>
   </si>
   <si>
+    <t>Supervising Attorney - Medical Legal Partnerships</t>
+  </si>
+  <si>
+    <t>Legal Clinic for the Disabled</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Legal Assistance, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/085b85b7a6ab4758afdff3f95ee0249d-supervising-attorney-medical-legal-partnerships-legal-clinic-for-the-disabled-philadelphia</t>
+  </si>
+  <si>
+    <t>Supported Education Counselor - Full Time</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea804f1ef7cc44c692386dc51bbdd146-supported-education-counselor-full-time-baltic-street-wellness-solutions-kings-county</t>
+  </si>
+  <si>
+    <t>Supported Employment Counselor</t>
+  </si>
+  <si>
+    <t>Job Path, Inc.</t>
+  </si>
+  <si>
+    <t>USD 43600.00 - 45600.00/year</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b0e0849f7214bae85dc8c86c7b24a73-supported-employment-counselor-job-path-inc-new-york</t>
+  </si>
+  <si>
     <t>US Audience Growth Consultant</t>
   </si>
   <si>
@@ -1822,9 +2692,6 @@
     <t>Vice President for Ocean Conservation</t>
   </si>
   <si>
-    <t>The Conservation Law Foundation</t>
-  </si>
-  <si>
     <t>USD 136000.00 - 180000.00/year</t>
   </si>
   <si>
@@ -1850,6 +2717,48 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/ef716bf1c0ce48fb957e74159f7ca20c-vice-president-of-community-engagement-conservation-colorado-denver</t>
+  </si>
+  <si>
+    <t>Vice President of Human Resources and Labor Relations</t>
+  </si>
+  <si>
+    <t>LA Opera</t>
+  </si>
+  <si>
+    <t>USD 250000.00 - 275000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/01ba83156c304008b17d88c3986d6580-vice-president-of-human-resources-and-labor-relations-la-opera-los-angeles</t>
+  </si>
+  <si>
+    <t>Vice President of Programs</t>
+  </si>
+  <si>
+    <t>The Housing Collective</t>
+  </si>
+  <si>
+    <t>Bridgeport, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/758fa97f6f424f088061e6e116a3a348-vice-president-of-programs-the-housing-collective-bridgeport</t>
+  </si>
+  <si>
+    <t>Video Producer/Animator and Editor</t>
+  </si>
+  <si>
+    <t>amfAR</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5cf01c1b60941aabca3c3ad9b4c9fc1-video-produceranimator-and-editor-amfar-new-york</t>
   </si>
   <si>
     <t>Voter Contact Field Director</t>
@@ -3416,7 +4325,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3455,8 +4364,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3464,7 +4399,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3505,1842 +4440,3406 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F4" t="s">
         <v>253</v>
       </c>
-      <c r="E4" t="s">
-        <v>260</v>
-      </c>
-      <c r="F4" t="s">
-        <v>247</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B5" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C5" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D5" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E5" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C6" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D6" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="E6" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F6" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B7" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C7" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D7" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E7" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F7" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C8" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D8" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="E8" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="F8" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>295</v>
       </c>
       <c r="D9" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="E9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="F9" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B10" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C10" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D10" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E10" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F10" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B11" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C11" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D11" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E11" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F11" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B12" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C12" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E12" t="s">
         <v>253</v>
       </c>
-      <c r="E12" t="s">
-        <v>306</v>
-      </c>
       <c r="F12" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B13" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="D13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E13" t="s">
         <v>253</v>
       </c>
-      <c r="E13" t="s">
-        <v>310</v>
-      </c>
       <c r="F13" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B14" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C14" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D14" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E14" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F14" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B15" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C15" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="D15" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E15" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="F15" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B16" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="C16" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="D16" t="s">
-        <v>253</v>
+        <v>336</v>
       </c>
       <c r="E16" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="F16" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B17" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="C17" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="D17" t="s">
+        <v>277</v>
+      </c>
+      <c r="E17" t="s">
         <v>253</v>
       </c>
-      <c r="E17" t="s">
-        <v>330</v>
-      </c>
       <c r="F17" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B18" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C18" t="s">
-        <v>335</v>
+        <v>251</v>
       </c>
       <c r="D18" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="E18" t="s">
-        <v>336</v>
+        <v>253</v>
       </c>
       <c r="F18" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B19" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C19" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D19" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E19" t="s">
-        <v>247</v>
+        <v>351</v>
       </c>
       <c r="F19" t="s">
-        <v>247</v>
+        <v>352</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B20" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C20" t="s">
-        <v>345</v>
+        <v>307</v>
       </c>
       <c r="D20" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E20" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="F20" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="B21" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C21" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="D21" t="s">
+        <v>259</v>
+      </c>
+      <c r="E21" t="s">
         <v>253</v>
       </c>
-      <c r="E21" t="s">
-        <v>352</v>
-      </c>
       <c r="F21" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C22" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="D22" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E22" t="s">
-        <v>358</v>
+        <v>253</v>
       </c>
       <c r="F22" t="s">
-        <v>247</v>
+        <v>362</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B23" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C23" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D23" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E23" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F23" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B24" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C24" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D24" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E24" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F24" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B25" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C25" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D25" t="s">
+        <v>259</v>
+      </c>
+      <c r="E25" t="s">
         <v>253</v>
       </c>
-      <c r="E25" t="s">
-        <v>346</v>
-      </c>
       <c r="F25" t="s">
-        <v>375</v>
+        <v>309</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B26" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C26" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="D26" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E26" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F26" t="s">
-        <v>247</v>
+        <v>385</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B27" t="s">
-        <v>383</v>
+        <v>306</v>
       </c>
       <c r="C27" t="s">
-        <v>384</v>
+        <v>307</v>
       </c>
       <c r="D27" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E27" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F27" t="s">
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B28" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C28" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="D28" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E28" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F28" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B29" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C29" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D29" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E29" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F29" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B30" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C30" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D30" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E30" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F30" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B31" t="s">
-        <v>406</v>
+        <v>349</v>
       </c>
       <c r="C31" t="s">
-        <v>407</v>
+        <v>350</v>
       </c>
       <c r="D31" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E31" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F31" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B32" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C32" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D32" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E32" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F32" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B33" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C33" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D33" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E33" t="s">
+        <v>415</v>
+      </c>
+      <c r="F33" t="s">
+        <v>416</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="F33" t="s">
-        <v>415</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B34" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C34" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D34" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E34" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F34" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B35" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C35" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D35" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="E35" t="s">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="F35" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B36" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C36" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D36" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E36" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F36" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B37" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C37" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D37" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="E37" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F37" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B38" t="s">
-        <v>406</v>
+        <v>445</v>
       </c>
       <c r="C38" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="D38" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E38" t="s">
-        <v>408</v>
+        <v>260</v>
       </c>
       <c r="F38" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B39" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C39" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D39" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E39" t="s">
-        <v>446</v>
+        <v>253</v>
       </c>
       <c r="F39" t="s">
-        <v>447</v>
+        <v>253</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B40" t="s">
-        <v>292</v>
+        <v>454</v>
       </c>
       <c r="C40" t="s">
-        <v>293</v>
+        <v>455</v>
       </c>
       <c r="D40" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E40" t="s">
-        <v>294</v>
+        <v>456</v>
       </c>
       <c r="F40" t="s">
-        <v>295</v>
+        <v>457</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="B41" t="s">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="C41" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="D41" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E41" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="F41" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B42" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="C42" t="s">
-        <v>176</v>
+        <v>467</v>
       </c>
       <c r="D42" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E42" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="F42" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="B43" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="C43" t="s">
-        <v>461</v>
+        <v>307</v>
       </c>
       <c r="D43" t="s">
+        <v>252</v>
+      </c>
+      <c r="E43" t="s">
+        <v>473</v>
+      </c>
+      <c r="F43" t="s">
         <v>253</v>
       </c>
-      <c r="E43" t="s">
-        <v>408</v>
-      </c>
-      <c r="F43" t="s">
-        <v>415</v>
-      </c>
       <c r="H43" s="2" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="B44" t="s">
-        <v>383</v>
+        <v>476</v>
       </c>
       <c r="C44" t="s">
-        <v>384</v>
+        <v>477</v>
       </c>
       <c r="D44" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E44" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="F44" t="s">
-        <v>386</v>
+        <v>479</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B45" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="C45" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="D45" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E45" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="F45" t="s">
-        <v>375</v>
+        <v>484</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="B46" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="C46" t="s">
-        <v>357</v>
+        <v>307</v>
       </c>
       <c r="D46" t="s">
+        <v>259</v>
+      </c>
+      <c r="E46" t="s">
+        <v>488</v>
+      </c>
+      <c r="F46" t="s">
         <v>253</v>
       </c>
-      <c r="E46" t="s">
-        <v>380</v>
-      </c>
-      <c r="F46" t="s">
-        <v>473</v>
-      </c>
       <c r="H46" s="2" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="B47" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="C47" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="D47" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E47" t="s">
-        <v>247</v>
+        <v>493</v>
       </c>
       <c r="F47" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B48" t="s">
-        <v>383</v>
+        <v>497</v>
       </c>
       <c r="C48" t="s">
-        <v>384</v>
+        <v>492</v>
       </c>
       <c r="D48" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E48" t="s">
-        <v>385</v>
+        <v>498</v>
       </c>
       <c r="F48" t="s">
-        <v>386</v>
+        <v>499</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="B49" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="C49" t="s">
-        <v>384</v>
+        <v>422</v>
       </c>
       <c r="D49" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E49" t="s">
-        <v>464</v>
+        <v>503</v>
       </c>
       <c r="F49" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="B50" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="C50" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="D50" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E50" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="F50" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="B51" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="C51" t="s">
-        <v>431</v>
+        <v>514</v>
       </c>
       <c r="D51" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E51" t="s">
-        <v>493</v>
+        <v>456</v>
       </c>
       <c r="F51" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="B52" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="C52" t="s">
-        <v>384</v>
+        <v>519</v>
       </c>
       <c r="D52" t="s">
+        <v>259</v>
+      </c>
+      <c r="E52" t="s">
+        <v>520</v>
+      </c>
+      <c r="F52" t="s">
         <v>253</v>
       </c>
-      <c r="E52" t="s">
-        <v>498</v>
-      </c>
-      <c r="F52" t="s">
-        <v>247</v>
-      </c>
       <c r="H52" s="2" t="s">
-        <v>499</v>
+        <v>521</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="B53" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="C53" t="s">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="D53" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E53" t="s">
-        <v>502</v>
+        <v>524</v>
       </c>
       <c r="F53" t="s">
-        <v>503</v>
+        <v>525</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>504</v>
+        <v>526</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="B54" t="s">
-        <v>506</v>
+        <v>528</v>
       </c>
       <c r="C54" t="s">
-        <v>507</v>
+        <v>529</v>
       </c>
       <c r="D54" t="s">
+        <v>259</v>
+      </c>
+      <c r="E54" t="s">
+        <v>530</v>
+      </c>
+      <c r="F54" t="s">
         <v>253</v>
       </c>
-      <c r="E54" t="s">
-        <v>247</v>
-      </c>
-      <c r="F54" t="s">
-        <v>508</v>
-      </c>
       <c r="H54" s="2" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="B55" t="s">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="C55" t="s">
-        <v>323</v>
+        <v>492</v>
       </c>
       <c r="D55" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E55" t="s">
-        <v>254</v>
+        <v>534</v>
       </c>
       <c r="F55" t="s">
-        <v>512</v>
+        <v>535</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>513</v>
+        <v>536</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>514</v>
+        <v>537</v>
       </c>
       <c r="B56" t="s">
-        <v>511</v>
+        <v>538</v>
       </c>
       <c r="C56" t="s">
-        <v>323</v>
+        <v>176</v>
       </c>
       <c r="D56" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E56" t="s">
-        <v>247</v>
+        <v>539</v>
       </c>
       <c r="F56" t="s">
-        <v>512</v>
+        <v>540</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="B57" t="s">
-        <v>501</v>
+        <v>543</v>
       </c>
       <c r="C57" t="s">
-        <v>335</v>
+        <v>492</v>
       </c>
       <c r="D57" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E57" t="s">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="F57" t="s">
-        <v>503</v>
+        <v>545</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>518</v>
+        <v>546</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="B58" t="s">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="C58" t="s">
-        <v>38</v>
+        <v>422</v>
       </c>
       <c r="D58" t="s">
-        <v>253</v>
+        <v>336</v>
       </c>
       <c r="E58" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F58" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>523</v>
+        <v>551</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>524</v>
+        <v>552</v>
       </c>
       <c r="B59" t="s">
-        <v>475</v>
+        <v>553</v>
       </c>
       <c r="C59" t="s">
-        <v>476</v>
+        <v>554</v>
       </c>
       <c r="D59" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E59" t="s">
-        <v>247</v>
+        <v>555</v>
       </c>
       <c r="F59" t="s">
-        <v>477</v>
+        <v>556</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>525</v>
+        <v>557</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>526</v>
+        <v>558</v>
       </c>
       <c r="B60" t="s">
-        <v>425</v>
+        <v>559</v>
       </c>
       <c r="C60" t="s">
-        <v>527</v>
+        <v>560</v>
       </c>
       <c r="D60" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="E60" t="s">
-        <v>396</v>
+        <v>561</v>
       </c>
       <c r="F60" t="s">
-        <v>427</v>
+        <v>357</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>528</v>
+        <v>562</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>529</v>
+        <v>558</v>
       </c>
       <c r="B61" t="s">
-        <v>530</v>
+        <v>563</v>
       </c>
       <c r="C61" t="s">
-        <v>452</v>
+        <v>564</v>
       </c>
       <c r="D61" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E61" t="s">
-        <v>531</v>
+        <v>565</v>
       </c>
       <c r="F61" t="s">
-        <v>532</v>
+        <v>566</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>533</v>
+        <v>567</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>534</v>
+        <v>568</v>
       </c>
       <c r="B62" t="s">
-        <v>535</v>
+        <v>569</v>
       </c>
       <c r="C62" t="s">
-        <v>384</v>
+        <v>570</v>
       </c>
       <c r="D62" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E62" t="s">
-        <v>536</v>
+        <v>571</v>
       </c>
       <c r="F62" t="s">
-        <v>537</v>
+        <v>572</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>538</v>
+        <v>573</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>539</v>
+        <v>574</v>
       </c>
       <c r="B63" t="s">
-        <v>540</v>
+        <v>575</v>
       </c>
       <c r="C63" t="s">
-        <v>357</v>
+        <v>576</v>
       </c>
       <c r="D63" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E63" t="s">
-        <v>247</v>
+        <v>577</v>
       </c>
       <c r="F63" t="s">
-        <v>267</v>
+        <v>370</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>542</v>
+        <v>579</v>
       </c>
       <c r="B64" t="s">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="C64" t="s">
-        <v>323</v>
+        <v>580</v>
       </c>
       <c r="D64" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E64" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="F64" t="s">
-        <v>545</v>
+        <v>370</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="B65" t="s">
-        <v>548</v>
+        <v>575</v>
       </c>
       <c r="C65" t="s">
-        <v>452</v>
+        <v>583</v>
       </c>
       <c r="D65" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E65" t="s">
-        <v>549</v>
+        <v>584</v>
       </c>
       <c r="F65" t="s">
-        <v>550</v>
+        <v>370</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>551</v>
+        <v>585</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>552</v>
+        <v>586</v>
       </c>
       <c r="B66" t="s">
-        <v>383</v>
+        <v>587</v>
       </c>
       <c r="C66" t="s">
-        <v>384</v>
+        <v>588</v>
       </c>
       <c r="D66" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="E66" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F66" t="s">
-        <v>554</v>
+        <v>589</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>555</v>
+        <v>590</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>556</v>
+        <v>591</v>
       </c>
       <c r="B67" t="s">
-        <v>557</v>
+        <v>592</v>
       </c>
       <c r="C67" t="s">
-        <v>558</v>
+        <v>593</v>
       </c>
       <c r="D67" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="E67" t="s">
-        <v>396</v>
+        <v>594</v>
       </c>
       <c r="F67" t="s">
-        <v>559</v>
+        <v>595</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>560</v>
+        <v>596</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>561</v>
+        <v>597</v>
       </c>
       <c r="B68" t="s">
-        <v>562</v>
+        <v>598</v>
       </c>
       <c r="C68" t="s">
-        <v>384</v>
+        <v>599</v>
       </c>
       <c r="D68" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="E68" t="s">
-        <v>380</v>
+        <v>600</v>
       </c>
       <c r="F68" t="s">
-        <v>563</v>
+        <v>601</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>564</v>
+        <v>602</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>565</v>
+        <v>603</v>
       </c>
       <c r="B69" t="s">
-        <v>566</v>
+        <v>604</v>
       </c>
       <c r="C69" t="s">
-        <v>567</v>
+        <v>605</v>
       </c>
       <c r="D69" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E69" t="s">
-        <v>536</v>
+        <v>606</v>
       </c>
       <c r="F69" t="s">
-        <v>568</v>
+        <v>607</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>569</v>
+        <v>608</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>570</v>
+        <v>609</v>
       </c>
       <c r="B70" t="s">
-        <v>571</v>
+        <v>610</v>
       </c>
       <c r="C70" t="s">
-        <v>452</v>
+        <v>611</v>
       </c>
       <c r="D70" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E70" t="s">
-        <v>572</v>
+        <v>612</v>
       </c>
       <c r="F70" t="s">
-        <v>573</v>
+        <v>613</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>574</v>
+        <v>614</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>575</v>
+        <v>615</v>
       </c>
       <c r="B71" t="s">
-        <v>576</v>
+        <v>616</v>
       </c>
       <c r="C71" t="s">
-        <v>357</v>
+        <v>617</v>
       </c>
       <c r="D71" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="E71" t="s">
-        <v>577</v>
+        <v>618</v>
       </c>
       <c r="F71" t="s">
-        <v>578</v>
+        <v>619</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>579</v>
+        <v>620</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>580</v>
+        <v>621</v>
       </c>
       <c r="B72" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="C72" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="D72" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E72" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="F72" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>585</v>
+        <v>622</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>586</v>
+        <v>623</v>
       </c>
       <c r="B73" t="s">
-        <v>587</v>
+        <v>624</v>
       </c>
       <c r="C73" t="s">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="D73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E73" t="s">
-        <v>589</v>
+        <v>626</v>
       </c>
       <c r="F73" t="s">
-        <v>590</v>
+        <v>627</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="B74" t="s">
-        <v>593</v>
+        <v>349</v>
       </c>
       <c r="C74" t="s">
-        <v>277</v>
+        <v>350</v>
       </c>
       <c r="D74" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E74" t="s">
-        <v>594</v>
+        <v>351</v>
       </c>
       <c r="F74" t="s">
-        <v>595</v>
+        <v>352</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>596</v>
+        <v>630</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>597</v>
+        <v>631</v>
       </c>
       <c r="B75" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="C75" t="s">
-        <v>357</v>
+        <v>632</v>
       </c>
       <c r="D75" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E75" t="s">
-        <v>247</v>
+        <v>633</v>
       </c>
       <c r="F75" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>600</v>
+        <v>634</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>601</v>
+        <v>635</v>
       </c>
       <c r="B76" t="s">
-        <v>602</v>
+        <v>636</v>
       </c>
       <c r="C76" t="s">
-        <v>335</v>
+        <v>176</v>
       </c>
       <c r="D76" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E76" t="s">
-        <v>603</v>
+        <v>637</v>
       </c>
       <c r="F76" t="s">
-        <v>604</v>
+        <v>638</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>605</v>
+        <v>639</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>606</v>
+        <v>640</v>
       </c>
       <c r="B77" t="s">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="C77" t="s">
-        <v>608</v>
+        <v>641</v>
       </c>
       <c r="D77" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E77" t="s">
-        <v>609</v>
+        <v>571</v>
       </c>
       <c r="F77" t="s">
-        <v>610</v>
+        <v>370</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>611</v>
+        <v>642</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="B78" t="s">
-        <v>613</v>
+        <v>533</v>
       </c>
       <c r="C78" t="s">
-        <v>614</v>
+        <v>492</v>
       </c>
       <c r="D78" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E78" t="s">
-        <v>615</v>
+        <v>644</v>
       </c>
       <c r="F78" t="s">
-        <v>247</v>
+        <v>535</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>616</v>
+        <v>645</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>617</v>
+        <v>646</v>
       </c>
       <c r="B79" t="s">
-        <v>618</v>
+        <v>647</v>
       </c>
       <c r="C79" t="s">
-        <v>619</v>
+        <v>648</v>
       </c>
       <c r="D79" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="E79" t="s">
-        <v>620</v>
+        <v>649</v>
       </c>
       <c r="F79" t="s">
-        <v>621</v>
+        <v>515</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>622</v>
+        <v>650</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="B80" t="s">
-        <v>283</v>
+        <v>652</v>
       </c>
       <c r="C80" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="D80" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="E80" t="s">
-        <v>247</v>
+        <v>520</v>
       </c>
       <c r="F80" t="s">
-        <v>289</v>
+        <v>653</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>624</v>
+        <v>654</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>625</v>
+        <v>651</v>
       </c>
       <c r="B81" t="s">
-        <v>283</v>
+        <v>655</v>
       </c>
       <c r="C81" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="D81" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="E81" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F81" t="s">
-        <v>627</v>
+        <v>657</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>628</v>
+        <v>658</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>651</v>
+      </c>
+      <c r="B82" t="s">
+        <v>659</v>
+      </c>
+      <c r="C82" t="s">
+        <v>492</v>
+      </c>
+      <c r="D82" t="s">
+        <v>259</v>
+      </c>
+      <c r="E82" t="s">
+        <v>660</v>
+      </c>
+      <c r="F82" t="s">
+        <v>253</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>662</v>
+      </c>
+      <c r="B83" t="s">
+        <v>663</v>
+      </c>
+      <c r="C83" t="s">
+        <v>307</v>
+      </c>
+      <c r="D83" t="s">
+        <v>259</v>
+      </c>
+      <c r="E83" t="s">
+        <v>664</v>
+      </c>
+      <c r="F83" t="s">
+        <v>665</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>667</v>
+      </c>
+      <c r="B84" t="s">
+        <v>668</v>
+      </c>
+      <c r="C84" t="s">
+        <v>307</v>
+      </c>
+      <c r="D84" t="s">
+        <v>259</v>
+      </c>
+      <c r="E84" t="s">
+        <v>669</v>
+      </c>
+      <c r="F84" t="s">
+        <v>670</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>672</v>
+      </c>
+      <c r="B85" t="s">
+        <v>533</v>
+      </c>
+      <c r="C85" t="s">
+        <v>492</v>
+      </c>
+      <c r="D85" t="s">
+        <v>259</v>
+      </c>
+      <c r="E85" t="s">
+        <v>534</v>
+      </c>
+      <c r="F85" t="s">
+        <v>535</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>674</v>
+      </c>
+      <c r="B86" t="s">
+        <v>675</v>
+      </c>
+      <c r="C86" t="s">
+        <v>492</v>
+      </c>
+      <c r="D86" t="s">
+        <v>259</v>
+      </c>
+      <c r="E86" t="s">
+        <v>644</v>
+      </c>
+      <c r="F86" t="s">
+        <v>676</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>678</v>
+      </c>
+      <c r="B87" t="s">
+        <v>679</v>
+      </c>
+      <c r="C87" t="s">
+        <v>680</v>
+      </c>
+      <c r="D87" t="s">
+        <v>259</v>
+      </c>
+      <c r="E87" t="s">
+        <v>681</v>
+      </c>
+      <c r="F87" t="s">
+        <v>682</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>684</v>
+      </c>
+      <c r="B88" t="s">
+        <v>685</v>
+      </c>
+      <c r="C88" t="s">
+        <v>599</v>
+      </c>
+      <c r="D88" t="s">
+        <v>259</v>
+      </c>
+      <c r="E88" t="s">
+        <v>686</v>
+      </c>
+      <c r="F88" t="s">
+        <v>687</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>689</v>
+      </c>
+      <c r="B89" t="s">
+        <v>690</v>
+      </c>
+      <c r="C89" t="s">
+        <v>611</v>
+      </c>
+      <c r="D89" t="s">
+        <v>277</v>
+      </c>
+      <c r="E89" t="s">
+        <v>691</v>
+      </c>
+      <c r="F89" t="s">
+        <v>692</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>694</v>
+      </c>
+      <c r="B90" t="s">
+        <v>695</v>
+      </c>
+      <c r="C90" t="s">
+        <v>329</v>
+      </c>
+      <c r="D90" t="s">
+        <v>259</v>
+      </c>
+      <c r="E90" t="s">
+        <v>696</v>
+      </c>
+      <c r="F90" t="s">
+        <v>697</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>699</v>
+      </c>
+      <c r="B91" t="s">
+        <v>700</v>
+      </c>
+      <c r="C91" t="s">
+        <v>492</v>
+      </c>
+      <c r="D91" t="s">
+        <v>259</v>
+      </c>
+      <c r="E91" t="s">
+        <v>701</v>
+      </c>
+      <c r="F91" t="s">
+        <v>253</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>703</v>
+      </c>
+      <c r="B92" t="s">
+        <v>704</v>
+      </c>
+      <c r="C92" t="s">
+        <v>492</v>
+      </c>
+      <c r="D92" t="s">
+        <v>277</v>
+      </c>
+      <c r="E92" t="s">
+        <v>705</v>
+      </c>
+      <c r="F92" t="s">
+        <v>706</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>708</v>
+      </c>
+      <c r="B93" t="s">
+        <v>709</v>
+      </c>
+      <c r="C93" t="s">
+        <v>440</v>
+      </c>
+      <c r="D93" t="s">
+        <v>259</v>
+      </c>
+      <c r="E93" t="s">
+        <v>710</v>
+      </c>
+      <c r="F93" t="s">
+        <v>711</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>713</v>
+      </c>
+      <c r="B94" t="s">
+        <v>714</v>
+      </c>
+      <c r="C94" t="s">
+        <v>715</v>
+      </c>
+      <c r="D94" t="s">
+        <v>259</v>
+      </c>
+      <c r="E94" t="s">
+        <v>253</v>
+      </c>
+      <c r="F94" t="s">
+        <v>716</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>718</v>
+      </c>
+      <c r="B95" t="s">
+        <v>317</v>
+      </c>
+      <c r="C95" t="s">
+        <v>719</v>
+      </c>
+      <c r="D95" t="s">
+        <v>259</v>
+      </c>
+      <c r="E95" t="s">
+        <v>253</v>
+      </c>
+      <c r="F95" t="s">
+        <v>319</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>718</v>
+      </c>
+      <c r="B96" t="s">
+        <v>317</v>
+      </c>
+      <c r="C96" t="s">
+        <v>719</v>
+      </c>
+      <c r="D96" t="s">
+        <v>259</v>
+      </c>
+      <c r="E96" t="s">
+        <v>253</v>
+      </c>
+      <c r="F96" t="s">
+        <v>319</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>722</v>
+      </c>
+      <c r="B97" t="s">
+        <v>723</v>
+      </c>
+      <c r="C97" t="s">
+        <v>422</v>
+      </c>
+      <c r="D97" t="s">
+        <v>259</v>
+      </c>
+      <c r="E97" t="s">
+        <v>260</v>
+      </c>
+      <c r="F97" t="s">
+        <v>724</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>726</v>
+      </c>
+      <c r="B98" t="s">
+        <v>723</v>
+      </c>
+      <c r="C98" t="s">
+        <v>422</v>
+      </c>
+      <c r="D98" t="s">
+        <v>259</v>
+      </c>
+      <c r="E98" t="s">
+        <v>253</v>
+      </c>
+      <c r="F98" t="s">
+        <v>724</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>728</v>
+      </c>
+      <c r="B99" t="s">
+        <v>379</v>
+      </c>
+      <c r="C99" t="s">
+        <v>380</v>
+      </c>
+      <c r="D99" t="s">
+        <v>259</v>
+      </c>
+      <c r="E99" t="s">
+        <v>253</v>
+      </c>
+      <c r="F99" t="s">
+        <v>729</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>731</v>
+      </c>
+      <c r="B100" t="s">
+        <v>732</v>
+      </c>
+      <c r="C100" t="s">
+        <v>733</v>
+      </c>
+      <c r="D100" t="s">
+        <v>259</v>
+      </c>
+      <c r="E100" t="s">
+        <v>734</v>
+      </c>
+      <c r="F100" t="s">
+        <v>735</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>737</v>
+      </c>
+      <c r="B101" t="s">
+        <v>709</v>
+      </c>
+      <c r="C101" t="s">
+        <v>440</v>
+      </c>
+      <c r="D101" t="s">
+        <v>259</v>
+      </c>
+      <c r="E101" t="s">
+        <v>738</v>
+      </c>
+      <c r="F101" t="s">
+        <v>711</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>740</v>
+      </c>
+      <c r="B102" t="s">
+        <v>741</v>
+      </c>
+      <c r="C102" t="s">
+        <v>38</v>
+      </c>
+      <c r="D102" t="s">
+        <v>259</v>
+      </c>
+      <c r="E102" t="s">
+        <v>742</v>
+      </c>
+      <c r="F102" t="s">
+        <v>743</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>745</v>
+      </c>
+      <c r="B103" t="s">
+        <v>746</v>
+      </c>
+      <c r="C103" t="s">
+        <v>747</v>
+      </c>
+      <c r="D103" t="s">
+        <v>259</v>
+      </c>
+      <c r="E103" t="s">
+        <v>748</v>
+      </c>
+      <c r="F103" t="s">
+        <v>749</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>751</v>
+      </c>
+      <c r="B104" t="s">
+        <v>655</v>
+      </c>
+      <c r="C104" t="s">
+        <v>656</v>
+      </c>
+      <c r="D104" t="s">
+        <v>259</v>
+      </c>
+      <c r="E104" t="s">
+        <v>253</v>
+      </c>
+      <c r="F104" t="s">
+        <v>657</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>753</v>
+      </c>
+      <c r="B105" t="s">
+        <v>587</v>
+      </c>
+      <c r="C105" t="s">
+        <v>754</v>
+      </c>
+      <c r="D105" t="s">
+        <v>277</v>
+      </c>
+      <c r="E105" t="s">
+        <v>555</v>
+      </c>
+      <c r="F105" t="s">
+        <v>589</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>756</v>
+      </c>
+      <c r="B106" t="s">
+        <v>757</v>
+      </c>
+      <c r="C106" t="s">
+        <v>632</v>
+      </c>
+      <c r="D106" t="s">
+        <v>284</v>
+      </c>
+      <c r="E106" t="s">
+        <v>758</v>
+      </c>
+      <c r="F106" t="s">
+        <v>759</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>761</v>
+      </c>
+      <c r="B107" t="s">
+        <v>528</v>
+      </c>
+      <c r="C107" t="s">
+        <v>529</v>
+      </c>
+      <c r="D107" t="s">
+        <v>259</v>
+      </c>
+      <c r="E107" t="s">
+        <v>762</v>
+      </c>
+      <c r="F107" t="s">
+        <v>763</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>765</v>
+      </c>
+      <c r="B108" t="s">
+        <v>766</v>
+      </c>
+      <c r="C108" t="s">
+        <v>307</v>
+      </c>
+      <c r="D108" t="s">
+        <v>259</v>
+      </c>
+      <c r="E108" t="s">
+        <v>253</v>
+      </c>
+      <c r="F108" t="s">
+        <v>442</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>768</v>
+      </c>
+      <c r="B109" t="s">
+        <v>769</v>
+      </c>
+      <c r="C109" t="s">
+        <v>307</v>
+      </c>
+      <c r="D109" t="s">
+        <v>336</v>
+      </c>
+      <c r="E109" t="s">
+        <v>253</v>
+      </c>
+      <c r="F109" t="s">
+        <v>254</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>768</v>
+      </c>
+      <c r="B110" t="s">
+        <v>769</v>
+      </c>
+      <c r="C110" t="s">
+        <v>307</v>
+      </c>
+      <c r="D110" t="s">
+        <v>336</v>
+      </c>
+      <c r="E110" t="s">
+        <v>253</v>
+      </c>
+      <c r="F110" t="s">
+        <v>254</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>772</v>
+      </c>
+      <c r="B111" t="s">
+        <v>773</v>
+      </c>
+      <c r="C111" t="s">
+        <v>492</v>
+      </c>
+      <c r="D111" t="s">
+        <v>259</v>
+      </c>
+      <c r="E111" t="s">
+        <v>774</v>
+      </c>
+      <c r="F111" t="s">
+        <v>775</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>777</v>
+      </c>
+      <c r="B112" t="s">
+        <v>778</v>
+      </c>
+      <c r="C112" t="s">
+        <v>307</v>
+      </c>
+      <c r="D112" t="s">
+        <v>259</v>
+      </c>
+      <c r="E112" t="s">
+        <v>253</v>
+      </c>
+      <c r="F112" t="s">
+        <v>286</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>780</v>
+      </c>
+      <c r="B113" t="s">
+        <v>781</v>
+      </c>
+      <c r="C113" t="s">
+        <v>422</v>
+      </c>
+      <c r="D113" t="s">
+        <v>259</v>
+      </c>
+      <c r="E113" t="s">
+        <v>384</v>
+      </c>
+      <c r="F113" t="s">
+        <v>782</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>784</v>
+      </c>
+      <c r="B114" t="s">
+        <v>785</v>
+      </c>
+      <c r="C114" t="s">
+        <v>422</v>
+      </c>
+      <c r="D114" t="s">
+        <v>259</v>
+      </c>
+      <c r="E114" t="s">
+        <v>786</v>
+      </c>
+      <c r="F114" t="s">
+        <v>545</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>788</v>
+      </c>
+      <c r="B115" t="s">
+        <v>789</v>
+      </c>
+      <c r="C115" t="s">
+        <v>632</v>
+      </c>
+      <c r="D115" t="s">
+        <v>259</v>
+      </c>
+      <c r="E115" t="s">
+        <v>790</v>
+      </c>
+      <c r="F115" t="s">
+        <v>791</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>793</v>
+      </c>
+      <c r="B116" t="s">
+        <v>766</v>
+      </c>
+      <c r="C116" t="s">
+        <v>307</v>
+      </c>
+      <c r="D116" t="s">
+        <v>259</v>
+      </c>
+      <c r="E116" t="s">
+        <v>253</v>
+      </c>
+      <c r="F116" t="s">
+        <v>442</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>795</v>
+      </c>
+      <c r="B117" t="s">
+        <v>746</v>
+      </c>
+      <c r="C117" t="s">
+        <v>796</v>
+      </c>
+      <c r="D117" t="s">
+        <v>259</v>
+      </c>
+      <c r="E117" t="s">
+        <v>797</v>
+      </c>
+      <c r="F117" t="s">
+        <v>749</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>799</v>
+      </c>
+      <c r="B118" t="s">
+        <v>533</v>
+      </c>
+      <c r="C118" t="s">
+        <v>492</v>
+      </c>
+      <c r="D118" t="s">
+        <v>259</v>
+      </c>
+      <c r="E118" t="s">
+        <v>800</v>
+      </c>
+      <c r="F118" t="s">
+        <v>801</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>803</v>
+      </c>
+      <c r="B119" t="s">
+        <v>804</v>
+      </c>
+      <c r="C119" t="s">
+        <v>805</v>
+      </c>
+      <c r="D119" t="s">
+        <v>277</v>
+      </c>
+      <c r="E119" t="s">
+        <v>555</v>
+      </c>
+      <c r="F119" t="s">
+        <v>806</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>808</v>
+      </c>
+      <c r="B120" t="s">
+        <v>809</v>
+      </c>
+      <c r="C120" t="s">
+        <v>492</v>
+      </c>
+      <c r="D120" t="s">
+        <v>259</v>
+      </c>
+      <c r="E120" t="s">
+        <v>520</v>
+      </c>
+      <c r="F120" t="s">
+        <v>810</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>812</v>
+      </c>
+      <c r="B121" t="s">
+        <v>813</v>
+      </c>
+      <c r="C121" t="s">
+        <v>611</v>
+      </c>
+      <c r="D121" t="s">
+        <v>259</v>
+      </c>
+      <c r="E121" t="s">
+        <v>774</v>
+      </c>
+      <c r="F121" t="s">
+        <v>814</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>816</v>
+      </c>
+      <c r="B122" t="s">
+        <v>306</v>
+      </c>
+      <c r="C122" t="s">
+        <v>817</v>
+      </c>
+      <c r="D122" t="s">
+        <v>259</v>
+      </c>
+      <c r="E122" t="s">
+        <v>818</v>
+      </c>
+      <c r="F122" t="s">
+        <v>819</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>821</v>
+      </c>
+      <c r="B123" t="s">
+        <v>822</v>
+      </c>
+      <c r="C123" t="s">
+        <v>632</v>
+      </c>
+      <c r="D123" t="s">
+        <v>259</v>
+      </c>
+      <c r="E123" t="s">
+        <v>271</v>
+      </c>
+      <c r="F123" t="s">
+        <v>823</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>825</v>
+      </c>
+      <c r="B124" t="s">
+        <v>826</v>
+      </c>
+      <c r="C124" t="s">
+        <v>307</v>
+      </c>
+      <c r="D124" t="s">
+        <v>259</v>
+      </c>
+      <c r="E124" t="s">
+        <v>827</v>
+      </c>
+      <c r="F124" t="s">
+        <v>828</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>830</v>
+      </c>
+      <c r="B125" t="s">
+        <v>831</v>
+      </c>
+      <c r="C125" t="s">
+        <v>832</v>
+      </c>
+      <c r="D125" t="s">
+        <v>259</v>
+      </c>
+      <c r="E125" t="s">
+        <v>833</v>
+      </c>
+      <c r="F125" t="s">
+        <v>834</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>830</v>
+      </c>
+      <c r="B126" t="s">
+        <v>831</v>
+      </c>
+      <c r="C126" t="s">
+        <v>836</v>
+      </c>
+      <c r="D126" t="s">
+        <v>259</v>
+      </c>
+      <c r="E126" t="s">
+        <v>833</v>
+      </c>
+      <c r="F126" t="s">
+        <v>834</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>830</v>
+      </c>
+      <c r="B127" t="s">
+        <v>838</v>
+      </c>
+      <c r="C127" t="s">
+        <v>839</v>
+      </c>
+      <c r="D127" t="s">
+        <v>259</v>
+      </c>
+      <c r="E127" t="s">
+        <v>296</v>
+      </c>
+      <c r="F127" t="s">
+        <v>840</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>830</v>
+      </c>
+      <c r="B128" t="s">
+        <v>842</v>
+      </c>
+      <c r="C128" t="s">
+        <v>733</v>
+      </c>
+      <c r="D128" t="s">
+        <v>259</v>
+      </c>
+      <c r="E128" t="s">
+        <v>843</v>
+      </c>
+      <c r="F128" t="s">
+        <v>840</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>830</v>
+      </c>
+      <c r="B129" t="s">
+        <v>845</v>
+      </c>
+      <c r="C129" t="s">
+        <v>846</v>
+      </c>
+      <c r="D129" t="s">
+        <v>259</v>
+      </c>
+      <c r="E129" t="s">
+        <v>847</v>
+      </c>
+      <c r="F129" t="s">
+        <v>848</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>830</v>
+      </c>
+      <c r="B130" t="s">
+        <v>845</v>
+      </c>
+      <c r="C130" t="s">
+        <v>850</v>
+      </c>
+      <c r="D130" t="s">
+        <v>259</v>
+      </c>
+      <c r="E130" t="s">
+        <v>847</v>
+      </c>
+      <c r="F130" t="s">
+        <v>848</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>830</v>
+      </c>
+      <c r="B131" t="s">
+        <v>845</v>
+      </c>
+      <c r="C131" t="s">
+        <v>852</v>
+      </c>
+      <c r="D131" t="s">
+        <v>259</v>
+      </c>
+      <c r="E131" t="s">
+        <v>847</v>
+      </c>
+      <c r="F131" t="s">
+        <v>848</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>830</v>
+      </c>
+      <c r="B132" t="s">
+        <v>845</v>
+      </c>
+      <c r="C132" t="s">
+        <v>854</v>
+      </c>
+      <c r="D132" t="s">
+        <v>259</v>
+      </c>
+      <c r="E132" t="s">
+        <v>847</v>
+      </c>
+      <c r="F132" t="s">
+        <v>848</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>856</v>
+      </c>
+      <c r="B133" t="s">
+        <v>857</v>
+      </c>
+      <c r="C133" t="s">
+        <v>858</v>
+      </c>
+      <c r="D133" t="s">
+        <v>259</v>
+      </c>
+      <c r="E133" t="s">
+        <v>859</v>
+      </c>
+      <c r="F133" t="s">
+        <v>860</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>862</v>
+      </c>
+      <c r="B134" t="s">
+        <v>863</v>
+      </c>
+      <c r="C134" t="s">
+        <v>864</v>
+      </c>
+      <c r="D134" t="s">
+        <v>259</v>
+      </c>
+      <c r="E134" t="s">
+        <v>405</v>
+      </c>
+      <c r="F134" t="s">
+        <v>447</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>866</v>
+      </c>
+      <c r="B135" t="s">
+        <v>867</v>
+      </c>
+      <c r="C135" t="s">
+        <v>868</v>
+      </c>
+      <c r="D135" t="s">
+        <v>277</v>
+      </c>
+      <c r="E135" t="s">
+        <v>278</v>
+      </c>
+      <c r="F135" t="s">
+        <v>253</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>870</v>
+      </c>
+      <c r="B136" t="s">
+        <v>842</v>
+      </c>
+      <c r="C136" t="s">
+        <v>335</v>
+      </c>
+      <c r="D136" t="s">
+        <v>259</v>
+      </c>
+      <c r="E136" t="s">
+        <v>871</v>
+      </c>
+      <c r="F136" t="s">
+        <v>872</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>874</v>
+      </c>
+      <c r="B137" t="s">
+        <v>875</v>
+      </c>
+      <c r="C137" t="s">
+        <v>570</v>
+      </c>
+      <c r="D137" t="s">
+        <v>259</v>
+      </c>
+      <c r="E137" t="s">
+        <v>876</v>
+      </c>
+      <c r="F137" t="s">
+        <v>877</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>879</v>
+      </c>
+      <c r="B138" t="s">
+        <v>746</v>
+      </c>
+      <c r="C138" t="s">
+        <v>796</v>
+      </c>
+      <c r="D138" t="s">
+        <v>259</v>
+      </c>
+      <c r="E138" t="s">
+        <v>880</v>
+      </c>
+      <c r="F138" t="s">
+        <v>749</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>882</v>
+      </c>
+      <c r="B139" t="s">
+        <v>883</v>
+      </c>
+      <c r="C139" t="s">
+        <v>492</v>
+      </c>
+      <c r="D139" t="s">
+        <v>259</v>
+      </c>
+      <c r="E139" t="s">
+        <v>884</v>
+      </c>
+      <c r="F139" t="s">
+        <v>885</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>887</v>
+      </c>
+      <c r="B140" t="s">
+        <v>888</v>
+      </c>
+      <c r="C140" t="s">
+        <v>307</v>
+      </c>
+      <c r="D140" t="s">
+        <v>252</v>
+      </c>
+      <c r="E140" t="s">
+        <v>253</v>
+      </c>
+      <c r="F140" t="s">
+        <v>889</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>891</v>
+      </c>
+      <c r="B141" t="s">
+        <v>379</v>
+      </c>
+      <c r="C141" t="s">
+        <v>440</v>
+      </c>
+      <c r="D141" t="s">
+        <v>259</v>
+      </c>
+      <c r="E141" t="s">
+        <v>892</v>
+      </c>
+      <c r="F141" t="s">
+        <v>893</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>895</v>
+      </c>
+      <c r="B142" t="s">
+        <v>896</v>
+      </c>
+      <c r="C142" t="s">
+        <v>897</v>
+      </c>
+      <c r="D142" t="s">
+        <v>259</v>
+      </c>
+      <c r="E142" t="s">
+        <v>898</v>
+      </c>
+      <c r="F142" t="s">
+        <v>899</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>901</v>
+      </c>
+      <c r="B143" t="s">
+        <v>902</v>
+      </c>
+      <c r="C143" t="s">
+        <v>335</v>
+      </c>
+      <c r="D143" t="s">
+        <v>259</v>
+      </c>
+      <c r="E143" t="s">
+        <v>903</v>
+      </c>
+      <c r="F143" t="s">
+        <v>469</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>905</v>
+      </c>
+      <c r="B144" t="s">
+        <v>906</v>
+      </c>
+      <c r="C144" t="s">
+        <v>907</v>
+      </c>
+      <c r="D144" t="s">
+        <v>259</v>
+      </c>
+      <c r="E144" t="s">
+        <v>908</v>
+      </c>
+      <c r="F144" t="s">
+        <v>357</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>910</v>
+      </c>
+      <c r="B145" t="s">
+        <v>911</v>
+      </c>
+      <c r="C145" t="s">
+        <v>258</v>
+      </c>
+      <c r="D145" t="s">
+        <v>259</v>
+      </c>
+      <c r="E145" t="s">
+        <v>912</v>
+      </c>
+      <c r="F145" t="s">
+        <v>913</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>915</v>
+      </c>
+      <c r="B146" t="s">
+        <v>916</v>
+      </c>
+      <c r="C146" t="s">
+        <v>917</v>
+      </c>
+      <c r="D146" t="s">
+        <v>284</v>
+      </c>
+      <c r="E146" t="s">
+        <v>918</v>
+      </c>
+      <c r="F146" t="s">
+        <v>253</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>920</v>
+      </c>
+      <c r="B147" t="s">
+        <v>921</v>
+      </c>
+      <c r="C147" t="s">
+        <v>922</v>
+      </c>
+      <c r="D147" t="s">
+        <v>336</v>
+      </c>
+      <c r="E147" t="s">
+        <v>923</v>
+      </c>
+      <c r="F147" t="s">
+        <v>924</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>926</v>
+      </c>
+      <c r="B148" t="s">
+        <v>341</v>
+      </c>
+      <c r="C148" t="s">
+        <v>342</v>
+      </c>
+      <c r="D148" t="s">
+        <v>277</v>
+      </c>
+      <c r="E148" t="s">
+        <v>253</v>
+      </c>
+      <c r="F148" t="s">
+        <v>346</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>928</v>
+      </c>
+      <c r="B149" t="s">
+        <v>341</v>
+      </c>
+      <c r="C149" t="s">
+        <v>929</v>
+      </c>
+      <c r="D149" t="s">
+        <v>277</v>
+      </c>
+      <c r="E149" t="s">
+        <v>253</v>
+      </c>
+      <c r="F149" t="s">
+        <v>930</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>931</v>
       </c>
     </row>
   </sheetData>
@@ -5426,6 +7925,74 @@
     <hyperlink ref="H79" r:id="rId78"/>
     <hyperlink ref="H80" r:id="rId79"/>
     <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
+    <hyperlink ref="H149" r:id="rId148"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
